--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -439,10 +439,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -458,7 +458,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Message: Front</t>
+          <t>Message: Pedal_Box</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Sender(s): Aquisition_board1</t>
+          <t>Sender(s): Aquisition_Board1</t>
         </is>
       </c>
     </row>
@@ -532,14 +532,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>APPS1</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -550,20 +550,16 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>100</v>
-      </c>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>bits</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr"/>
@@ -571,14 +567,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>hydraulic_brake_pressure</t>
+          <t>APPS2</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -589,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -598,125 +594,129 @@
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>bits</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>bots</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6"/>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Message: Front_Wheel_L</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x720</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board2</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Message: F_left</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x720</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_board2</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>wheel_speed</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Km/h</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>wheel_speed</t>
+          <t>tire_temp</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>8</v>
@@ -739,7 +739,7 @@
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Km/h</t>
+          <t>º</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
@@ -747,11 +747,11 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>tire_temp</t>
+          <t>Brake_disc_temp</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>8</v>
@@ -782,11 +782,11 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Brake_disc_temp</t>
+          <t>wheel_angle</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>8</v>
@@ -814,124 +814,120 @@
       </c>
       <c r="K11" s="3" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>wheel_angle</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C12" s="3" t="n">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Message: Front_Wheel_R</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x730</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>wheel_speed</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>º</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Message: F_right</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x730</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_board3</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>wheel_speed</t>
+          <t>tire_temp</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>8</v>
@@ -958,11 +954,11 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>tire_temp</t>
+          <t>Brake_disc_temp</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>8</v>
@@ -989,11 +985,11 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Brake_disc_temp</t>
+          <t>wheel_angle</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>8</v>
@@ -1017,120 +1013,120 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>wheel_angle</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20"/>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Message: Data_Box</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x740</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board4</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>Message: data_box</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x740</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_board4</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>suspension_level_left</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
+      <c r="J22" s="3" t="n"/>
+      <c r="K22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>suspension_level_left</t>
+          <t>suspension_level_right</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>16</v>
@@ -1154,120 +1150,120 @@
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="inlineStr"/>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>suspension_level_right</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25"/>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Message: Rear_Wheel_L</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x750</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board5</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>Message: Side_panel</t>
-        </is>
-      </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x750</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_board7</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Shutdown_circuit</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Shutdown_circuit</t>
+          <t>mission_select</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>1</v>
@@ -1294,11 +1290,11 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>mission_select</t>
+          <t>ignition</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>1</v>
@@ -1322,123 +1318,127 @@
       <c r="J29" s="3" t="n"/>
       <c r="K29" s="3" t="inlineStr"/>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>ignition</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="3" t="n"/>
-      <c r="I30" s="3" t="n"/>
-      <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="inlineStr"/>
-    </row>
-    <row r="31"/>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Message: Rear_Wheel_R</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x760</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board6</t>
+        </is>
+      </c>
+    </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>Message: Rear_pressure</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x760</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_board8</t>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Hydrauli_brake_pressure</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Hydrauli_brake_pressure</t>
+          <t>NTC1</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
       <c r="I34" s="3" t="n"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>º</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr"/>
@@ -1466,11 +1466,11 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>NTC1</t>
+          <t>NTC2</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>8</v>
@@ -1501,11 +1501,11 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>NTC2</t>
+          <t>NTC3</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>8</v>
@@ -1536,11 +1536,11 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>NTC3</t>
+          <t>NTC4</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>8</v>
@@ -1571,11 +1571,11 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>NTC4</t>
+          <t>NTC5</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>8</v>
@@ -1606,11 +1606,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>NTC5</t>
+          <t>NTC6</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>8</v>
@@ -1638,127 +1638,123 @@
       </c>
       <c r="K39" s="3" t="inlineStr"/>
     </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>NTC6</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C40" s="3" t="n">
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Message: Central_Rear</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x8</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>wheel_speed</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="n"/>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>º</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr"/>
-    </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>Message: Rear_left</t>
-        </is>
-      </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x8</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_board6</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" s="3" t="n"/>
+      <c r="K43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>wheel_speed</t>
+          <t>Tire_temp</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
@@ -1769,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>0</v>
@@ -1782,11 +1778,11 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Tire_temp</t>
+          <t>Brake_disk_temp</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>16</v>
@@ -1809,37 +1805,6 @@
       <c r="I45" s="3" t="n"/>
       <c r="J45" s="3" t="n"/>
       <c r="K45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Brake_disk_temp</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="3" t="n"/>
-      <c r="I46" s="3" t="n"/>
-      <c r="J46" s="3" t="n"/>
-      <c r="K46" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1852,12 +1817,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -2610,6 +2575,680 @@
       </c>
       <c r="K22" s="3" t="inlineStr"/>
     </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT1</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x710</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>BRK_PRESS</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="n"/>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>BOTS</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT2</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x720</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>WHEEL_ANGLE</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>º</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT3</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x730</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>WHEEL_ANGLE</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="3" t="n"/>
+      <c r="I36" s="3" t="n"/>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>º</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT4</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x740</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>ST_ANGLE</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3" t="n"/>
+      <c r="I40" s="3" t="n"/>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>º</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>INERTIA</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="n"/>
+      <c r="K41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>EMER_BUTTON</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3" t="n"/>
+      <c r="I42" s="3" t="n"/>
+      <c r="J42" s="3" t="n"/>
+      <c r="K42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT7</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x770</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board7</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>BRK_PRESS</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3" t="n"/>
+      <c r="I46" s="3" t="n"/>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2621,12 +3260,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1042"/>
+  <dimension ref="A1:K1052"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -35013,6 +35652,288 @@
       </c>
       <c r="K1042" s="3" t="inlineStr"/>
     </row>
+    <row r="1043"/>
+    <row r="1044">
+      <c r="A1044" s="1" t="inlineStr">
+        <is>
+          <t>Message: APPS_ADC_Raw</t>
+        </is>
+      </c>
+      <c r="B1044" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x710</t>
+        </is>
+      </c>
+      <c r="C1044" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B1045" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C1045" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D1045" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E1045" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F1045" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G1045" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H1045" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I1045" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J1045" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K1045" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="3" t="inlineStr">
+        <is>
+          <t>APPS1</t>
+        </is>
+      </c>
+      <c r="B1046" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1046" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1046" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E1046" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F1046" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G1046" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1046" s="3" t="n"/>
+      <c r="I1046" s="3" t="n"/>
+      <c r="J1046" s="3" t="inlineStr">
+        <is>
+          <t>bits</t>
+        </is>
+      </c>
+      <c r="K1046" s="3" t="inlineStr"/>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="3" t="inlineStr">
+        <is>
+          <t>APPS2</t>
+        </is>
+      </c>
+      <c r="B1047" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1047" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1047" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E1047" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F1047" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G1047" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1047" s="3" t="n"/>
+      <c r="I1047" s="3" t="n"/>
+      <c r="J1047" s="3" t="inlineStr">
+        <is>
+          <t>bits</t>
+        </is>
+      </c>
+      <c r="K1047" s="3" t="inlineStr"/>
+    </row>
+    <row r="1048"/>
+    <row r="1049">
+      <c r="A1049" s="1" t="inlineStr">
+        <is>
+          <t>Message: DashBoard</t>
+        </is>
+      </c>
+      <c r="B1049" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x740</t>
+        </is>
+      </c>
+      <c r="C1049" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B1050" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C1050" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D1050" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E1050" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F1050" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G1050" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H1050" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I1050" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J1050" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K1050" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="3" t="inlineStr">
+        <is>
+          <t>Ignition</t>
+        </is>
+      </c>
+      <c r="B1051" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1051" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1051" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E1051" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F1051" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1051" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1051" s="3" t="n"/>
+      <c r="I1051" s="3" t="n"/>
+      <c r="J1051" s="3" t="n"/>
+      <c r="K1051" s="3" t="inlineStr"/>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="3" t="inlineStr">
+        <is>
+          <t>Ready_To_Drive</t>
+        </is>
+      </c>
+      <c r="B1052" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1052" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1052" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E1052" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F1052" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1052" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1052" s="3" t="n"/>
+      <c r="I1052" s="3" t="n"/>
+      <c r="J1052" s="3" t="n"/>
+      <c r="K1052" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="aquisition_boards" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="autonomous_t26" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="powertrain_t26" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="data_t26" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="aquisition_boards" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="autonomous_t26" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="powertrain_t26" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,6 +440,1077 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT2</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x720</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>SPD_WHEEL</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>TIRE_TEMP</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>BRAKE_TEMP</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT3</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x730</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>SPD_WHEEL</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>TIRE_TEMP</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>BRAKE_TEMP</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT5</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x750</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>SPD_WHEEL</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>TIRE_TEMP</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>BRAKE_TEMP</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT6</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x760</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>SPD_WHEEL</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>TIRE_TEMP</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>BRAKE_TEMP</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT7_1</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x770</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board7</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>NTC_1</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>NTC_2</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>NTC_3</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT7_2</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x775</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>SUSP_R</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>SUSP_L</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="n"/>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1811,7 +2883,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3254,7 +4326,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -35692,7 +35692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -36069,7 +36069,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>º</t>
+          <t>ï¿½</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
@@ -36183,7 +36183,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>º</t>
+          <t>ï¿½</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr"/>
@@ -36296,7 +36296,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>º</t>
+          <t>ï¿½</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
@@ -36445,7 +36445,7 @@
       <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>º</t>
+          <t>ï¿½</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr"/>
@@ -36727,7 +36727,7 @@
       <c r="I32" s="3" t="n"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>º</t>
+          <t>ï¿½</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr"/>
@@ -36837,7 +36837,7 @@
       <c r="I36" s="3" t="n"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>º</t>
+          <t>ï¿½</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr"/>
@@ -36947,7 +36947,7 @@
       <c r="I40" s="3" t="n"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>º</t>
+          <t>ï¿½</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr"/>
@@ -37124,6 +37124,611 @@
       </c>
       <c r="K46" s="3" t="inlineStr"/>
     </row>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_IGN_R2D</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x600</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>ignition_manual</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="3" t="n"/>
+      <c r="I50" s="3" t="n"/>
+      <c r="J50" s="3" t="n"/>
+      <c r="K50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>r2d_manual</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" s="3" t="n"/>
+      <c r="J51" s="3" t="n"/>
+      <c r="K51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>ignition_auto</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="n"/>
+      <c r="I52" s="3" t="n"/>
+      <c r="J52" s="3" t="n"/>
+      <c r="K52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>r2d_auto</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3" t="n"/>
+      <c r="I53" s="3" t="n"/>
+      <c r="J53" s="3" t="n"/>
+      <c r="K53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>shutdown_signal</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3" t="n"/>
+      <c r="I54" s="3" t="n"/>
+      <c r="J54" s="3" t="n"/>
+      <c r="K54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>vcu_state</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3" t="n"/>
+      <c r="I55" s="3" t="n"/>
+      <c r="J55" s="3" t="n"/>
+      <c r="K55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>R2D_button_raw</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3" t="n"/>
+      <c r="I56" s="3" t="n"/>
+      <c r="J56" s="3" t="n"/>
+      <c r="K56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Ignition_switch_raw</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3" t="n"/>
+      <c r="I57" s="3" t="n"/>
+      <c r="J57" s="3" t="n"/>
+      <c r="K57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_HV</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x81</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3" t="n"/>
+      <c r="I61" s="3" t="n"/>
+      <c r="J61" s="3" t="n"/>
+      <c r="K61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Brake_pressure_Front</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3" t="n"/>
+      <c r="I62" s="3" t="n"/>
+      <c r="J62" s="3" t="n"/>
+      <c r="K62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Brake_pressure_Rear</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="3" t="n"/>
+      <c r="I63" s="3" t="n"/>
+      <c r="J63" s="3" t="n"/>
+      <c r="K63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64"/>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_RPM</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x509</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>rpm_actual</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -35692,20 +35692,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
     <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="130" customWidth="1" min="11" max="11"/>
+    <col width="129" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36078,7 +36078,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Message: dir_actuator_feedback</t>
+          <t>Message: CubeMars_Feedback</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
@@ -36088,7 +36088,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>Sender(s): AK10_9</t>
+          <t>Sender(s): Unknown</t>
         </is>
       </c>
     </row>
@@ -36156,34 +36156,34 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>16</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E14" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>-32000</v>
+        <v>-3200</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>32000</v>
+        <v>3200</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>ï¿½</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr"/>
@@ -36191,38 +36191,38 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Speed</t>
+          <t>Speed_RPM</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>16</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E15" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>210</v>
+        <v>1890</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>-32000</v>
+        <v>-320000</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>32000</v>
+        <v>320000</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>ERPM</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr"/>
@@ -36234,27 +36234,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>16</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E16" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>100</v>
+        <v>0.01</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
+      <c r="H16" s="3" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>60</v>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
           <t>A</t>
@@ -36265,22 +36269,22 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Driver_Temp</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>8</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E17" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>1</v>
@@ -36296,7 +36300,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>ï¿½</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
@@ -36304,18 +36308,18 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Error_codes</t>
+          <t>Error_Code</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>8</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E18" s="3" t="b">
@@ -36331,20 +36335,16 @@
         <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>7</v>
+        <v>255</v>
       </c>
       <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>0=No Fault, 1=Motor Over-temperature, 2=Over-current, 3=Over-voltage, 4=Encode Fault, 5=Mosfet Over-temperature, 6=Motor Lock-up</t>
-        </is>
-      </c>
+      <c r="K18" s="3" t="inlineStr"/>
     </row>
     <row r="19"/>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Message: dir_act_possition_loop</t>
+          <t>Message: CubeMars_possition_loop</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
@@ -37729,6 +37729,362 @@
       </c>
       <c r="K67" s="3" t="inlineStr"/>
     </row>
+    <row r="68"/>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>Message: JETSON</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x61</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>AS_STATE</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J71" s="3" t="n"/>
+      <c r="K71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>AS_MISSION</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J72" s="3" t="n"/>
+      <c r="K72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>TEMPERATURE</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J73" s="3" t="n"/>
+      <c r="K73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J74" s="3" t="n"/>
+      <c r="K74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J75" s="3" t="n"/>
+      <c r="K75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76"/>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>Message: RES</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x191</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>SIGNAL</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="3" t="n"/>
+      <c r="I79" s="3" t="n"/>
+      <c r="J79" s="3" t="n"/>
+      <c r="K79" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="powertrain_t26" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="data_t26" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="aquisition_boards" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="autonomous_t26" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="autonomous_t26" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="powertrain_t26" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="data_t26" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="aquisition_boards" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,6 +440,2410 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="129" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Message: ACU</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x51</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ACU</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>IGN</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>0=OFF, 1=ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ASMS</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>0=OFF, 1=ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>EMERGENCY</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>0=OFF, 1=ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>AS_STATE</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>1=OFF, 2=READY, 3=DRIVING, 4=EMERGENCY, 5=FINISH</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Mission_select</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>ACU_STATE</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>0=INIT, 1=MISSION_SELECT, 2=JETSON_WAITING, 3=INIT_SEQUENCE, 4=READY, 5=DRIVING, 6=EBS_ERROR, 7=EMERGENCY, 8=FINISHED, 9=MANUAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>ASSI_STATE</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>1=OFF, 2=READY, 3=DRIVING, 4=EMERGENCY, 5=FINISH</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>ACU_CPU_TEMP</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Message: CubeMars_Feedback</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x2968</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>-3200</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Speed_RPM</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>1890</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>-320000</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>320000</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>ERPM</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Driver_Temp</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Error_Code</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Message: CubeMars_possition_loop</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x468</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>POSITION</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT1</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x710</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>BRK_PRESS</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="n"/>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>BOTS</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT2</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x720</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>WHEEL_ANGLE</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT3</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x730</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>WHEEL_ANGLE</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="3" t="n"/>
+      <c r="I36" s="3" t="n"/>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT4</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x740</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>ST_ANGLE</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3" t="n"/>
+      <c r="I40" s="3" t="n"/>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>INERTIA</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="n"/>
+      <c r="K41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>EMER_BUTTON</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3" t="n"/>
+      <c r="I42" s="3" t="n"/>
+      <c r="J42" s="3" t="n"/>
+      <c r="K42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT7</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x770</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board7</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>BRK_PRESS</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3" t="n"/>
+      <c r="I46" s="3" t="n"/>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_IGN_R2D</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x600</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>ignition_manual</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="3" t="n"/>
+      <c r="I50" s="3" t="n"/>
+      <c r="J50" s="3" t="n"/>
+      <c r="K50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>r2d_manual</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" s="3" t="n"/>
+      <c r="J51" s="3" t="n"/>
+      <c r="K51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>ignition_auto</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="n"/>
+      <c r="I52" s="3" t="n"/>
+      <c r="J52" s="3" t="n"/>
+      <c r="K52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>r2d_auto</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3" t="n"/>
+      <c r="I53" s="3" t="n"/>
+      <c r="J53" s="3" t="n"/>
+      <c r="K53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>shutdown_signal</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3" t="n"/>
+      <c r="I54" s="3" t="n"/>
+      <c r="J54" s="3" t="n"/>
+      <c r="K54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>vcu_state</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3" t="n"/>
+      <c r="I55" s="3" t="n"/>
+      <c r="J55" s="3" t="n"/>
+      <c r="K55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>R2D_button_raw</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3" t="n"/>
+      <c r="I56" s="3" t="n"/>
+      <c r="J56" s="3" t="n"/>
+      <c r="K56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Ignition_switch_raw</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3" t="n"/>
+      <c r="I57" s="3" t="n"/>
+      <c r="J57" s="3" t="n"/>
+      <c r="K57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_HV</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x81</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3" t="n"/>
+      <c r="I61" s="3" t="n"/>
+      <c r="J61" s="3" t="n"/>
+      <c r="K61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Brake_pressure_Front</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3" t="n"/>
+      <c r="I62" s="3" t="n"/>
+      <c r="J62" s="3" t="n"/>
+      <c r="K62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Brake_pressure_Rear</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="3" t="n"/>
+      <c r="I63" s="3" t="n"/>
+      <c r="J63" s="3" t="n"/>
+      <c r="K63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64"/>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_RPM</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x509</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>rpm_actual</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68"/>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>Message: JETSON</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x61</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>AS_STATE</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J71" s="3" t="n"/>
+      <c r="K71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>AS_MISSION</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J72" s="3" t="n"/>
+      <c r="K72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>TEMPERATURE</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J73" s="3" t="n"/>
+      <c r="K73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J74" s="3" t="n"/>
+      <c r="K74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J75" s="3" t="n"/>
+      <c r="K75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76"/>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>Message: RES</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x191</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>SIGNAL</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="3" t="n"/>
+      <c r="I79" s="3" t="n"/>
+      <c r="J79" s="3" t="n"/>
+      <c r="K79" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K1056"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2030,12 +4434,12 @@
         <v>0</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J51" s="3" t="n"/>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+          <t>0=No open wire, 1=Cell 1, 2=Cell 2, 3=Cell 3, 4=Cell 4, 5=Cell 5, 6=Cell 6, 7=Cell 7, 8=Cell 8, 9=Cell 9, 10=Cell 10, 11=Cell 11, 12=Cell 12, 13=GPIO 1, 14=GPIO 2, 15=GPIO 3, 16=GPIO 4, 17=GPIO 5, 18=GPIO 6</t>
         </is>
       </c>
     </row>
@@ -3644,12 +6048,12 @@
         <v>0</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J103" s="3" t="n"/>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+          <t>0=No open wire, 1=Cell 1, 2=Cell 2, 3=Cell 3, 4=Cell 4, 5=Cell 5, 6=Cell 6, 7=Cell 7, 8=Cell 8, 9=Cell 9, 10=Cell 10, 11=Cell 11, 12=Cell 12, 13=GPIO 1, 14=GPIO 2, 15=GPIO 3, 16=GPIO 4, 17=GPIO 5, 18=GPIO 6</t>
         </is>
       </c>
     </row>
@@ -5258,12 +7662,12 @@
         <v>0</v>
       </c>
       <c r="I155" s="3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J155" s="3" t="n"/>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+          <t>0=No open wire, 1=Cell 1, 2=Cell 2, 3=Cell 3, 4=Cell 4, 5=Cell 5, 6=Cell 6, 7=Cell 7, 8=Cell 8, 9=Cell 9, 10=Cell 10, 11=Cell 11, 12=Cell 12, 13=GPIO 1, 14=GPIO 2, 15=GPIO 3, 16=GPIO 4, 17=GPIO 5, 18=GPIO 6</t>
         </is>
       </c>
     </row>
@@ -6767,12 +9171,12 @@
         <v>0</v>
       </c>
       <c r="I204" s="3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J204" s="3" t="n"/>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+          <t>0=No open wire, 1=Cell 1, 2=Cell 2, 3=Cell 3, 4=Cell 4, 5=Cell 5, 6=Cell 6, 7=Cell 7, 8=Cell 8, 9=Cell 9, 10=Cell 10, 11=Cell 11, 12=Cell 12, 13=GPIO 1, 14=GPIO 2, 15=GPIO 3, 16=GPIO 4, 17=GPIO 5, 18=GPIO 6</t>
         </is>
       </c>
     </row>
@@ -8276,12 +10680,12 @@
         <v>0</v>
       </c>
       <c r="I253" s="3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J253" s="3" t="n"/>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>0=No fault detected, 1=Cell/open-wire /voltage diagnostic fault</t>
+          <t>0=No open wire, 1=Cell 1, 2=Cell 2, 3=Cell 3, 4=Cell 4, 5=Cell 5, 6=Cell 6, 7=Cell 7, 8=Cell 8, 9=Cell 9, 10=Cell 10, 11=Cell 11, 12=Cell 12, 13=GPIO 1, 14=GPIO 2, 15=GPIO 3, 16=GPIO 4, 17=GPIO 5, 18=GPIO 6</t>
         </is>
       </c>
     </row>
@@ -9785,12 +12189,12 @@
         <v>0</v>
       </c>
       <c r="I302" s="3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J302" s="3" t="n"/>
       <c r="K302" s="3" t="inlineStr">
         <is>
-          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+          <t>0=No open wire, 1=Cell 1, 2=Cell 2, 3=Cell 3, 4=Cell 4, 5=Cell 5, 6=Cell 6, 7=Cell 7, 8=Cell 8, 9=Cell 9, 10=Cell 10, 11=Cell 11, 12=Cell 12, 13=GPIO 1, 14=GPIO 2, 15=GPIO 3, 16=GPIO 4, 17=GPIO 5, 18=GPIO 6</t>
         </is>
       </c>
     </row>
@@ -11294,12 +13698,12 @@
         <v>0</v>
       </c>
       <c r="I351" s="3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J351" s="3" t="n"/>
       <c r="K351" s="3" t="inlineStr">
         <is>
-          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+          <t>0=No open wire, 1=Cell 1, 2=Cell 2, 3=Cell 3, 4=Cell 4, 5=Cell 5, 6=Cell 6, 7=Cell 7, 8=Cell 8, 9=Cell 9, 10=Cell 10, 11=Cell 11, 12=Cell 12, 13=GPIO 1, 14=GPIO 2, 15=GPIO 3, 16=GPIO 4, 17=GPIO 5, 18=GPIO 6</t>
         </is>
       </c>
     </row>
@@ -12803,12 +15207,12 @@
         <v>0</v>
       </c>
       <c r="I400" s="3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J400" s="3" t="n"/>
       <c r="K400" s="3" t="inlineStr">
         <is>
-          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+          <t>0=No open wire, 1=Cell 1, 2=Cell 2, 3=Cell 3, 4=Cell 4, 5=Cell 5, 6=Cell 6, 7=Cell 7, 8=Cell 8, 9=Cell 9, 10=Cell 10, 11=Cell 11, 12=Cell 12, 13=GPIO 1, 14=GPIO 2, 15=GPIO 3, 16=GPIO 4, 17=GPIO 5, 18=GPIO 6</t>
         </is>
       </c>
     </row>
@@ -14312,12 +16716,12 @@
         <v>0</v>
       </c>
       <c r="I449" s="3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J449" s="3" t="n"/>
       <c r="K449" s="3" t="inlineStr">
         <is>
-          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+          <t>0=No open wire, 1=Cell 1, 2=Cell 2, 3=Cell 3, 4=Cell 4, 5=Cell 5, 6=Cell 6, 7=Cell 7, 8=Cell 8, 9=Cell 9, 10=Cell 10, 11=Cell 11, 12=Cell 12, 13=GPIO 1, 14=GPIO 2, 15=GPIO 3, 16=GPIO 4, 17=GPIO 5, 18=GPIO 6</t>
         </is>
       </c>
     </row>
@@ -15821,12 +18225,12 @@
         <v>0</v>
       </c>
       <c r="I498" s="3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J498" s="3" t="n"/>
       <c r="K498" s="3" t="inlineStr">
         <is>
-          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+          <t>0=No open wire, 1=Cell 1, 2=Cell 2, 3=Cell 3, 4=Cell 4, 5=Cell 5, 6=Cell 6, 7=Cell 7, 8=Cell 8, 9=Cell 9, 10=Cell 10, 11=Cell 11, 12=Cell 12, 13=GPIO 1, 14=GPIO 2, 15=GPIO 3, 16=GPIO 4, 17=GPIO 5, 18=GPIO 6</t>
         </is>
       </c>
     </row>
@@ -17330,12 +19734,12 @@
         <v>0</v>
       </c>
       <c r="I547" s="3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J547" s="3" t="n"/>
       <c r="K547" s="3" t="inlineStr">
         <is>
-          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+          <t>0=No open wire, 1=Cell 1, 2=Cell 2, 3=Cell 3, 4=Cell 4, 5=Cell 5, 6=Cell 6, 7=Cell 7, 8=Cell 8, 9=Cell 9, 10=Cell 10, 11=Cell 11, 12=Cell 12, 13=GPIO 1, 14=GPIO 2, 15=GPIO 3, 16=GPIO 4, 17=GPIO 5, 18=GPIO 6</t>
         </is>
       </c>
     </row>
@@ -18839,12 +21243,12 @@
         <v>0</v>
       </c>
       <c r="I596" s="3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J596" s="3" t="n"/>
       <c r="K596" s="3" t="inlineStr">
         <is>
-          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+          <t>0=No open wire, 1=Cell 1, 2=Cell 2, 3=Cell 3, 4=Cell 4, 5=Cell 5, 6=Cell 6, 7=Cell 7, 8=Cell 8, 9=Cell 9, 10=Cell 10, 11=Cell 11, 12=Cell 12, 13=GPIO 1, 14=GPIO 2, 15=GPIO 3, 16=GPIO 4, 17=GPIO 5, 18=GPIO 6</t>
         </is>
       </c>
     </row>
@@ -33237,7 +35641,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34308,7 +36712,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35684,2408 +38088,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K79"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="129" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Message: ACU</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x51</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ACU</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>IGN</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>0=OFF, 1=ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>ASMS</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>0=OFF, 1=ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>EMERGENCY</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>0=OFF, 1=ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>AS_STATE</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>1=OFF, 2=READY, 3=DRIVING, 4=EMERGENCY, 5=FINISH</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Mission_select</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>ACU_STATE</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>0=INIT, 1=MISSION_SELECT, 2=JETSON_WAITING, 3=INIT_SEQUENCE, 4=READY, 5=DRIVING, 6=EBS_ERROR, 7=EMERGENCY, 8=FINISHED, 9=MANUAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>ASSI_STATE</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>1=OFF, 2=READY, 3=DRIVING, 4=EMERGENCY, 5=FINISH</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>ACU_CPU_TEMP</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Message: CubeMars_Feedback</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x2968</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>-3200</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>3200</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Speed_RPM</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>1890</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>-320000</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>320000</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>ERPM</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>-60</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Driver_Temp</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>degC</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Error_Code</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Message: CubeMars_possition_loop</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x468</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): JETSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>POSITION</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT1</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x710</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board1</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>BRK_PRESS</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="3" t="n"/>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>RES</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>BOTS</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
-      <c r="J28" s="3" t="n"/>
-      <c r="K28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT2</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x720</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>WHEEL_ANGLE</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3" t="n"/>
-      <c r="I32" s="3" t="n"/>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr"/>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT3</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x730</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board3</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>WHEEL_ANGLE</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="3" t="n"/>
-      <c r="I36" s="3" t="n"/>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr"/>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT4</t>
-        </is>
-      </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x740</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board4</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>ST_ANGLE</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="n"/>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>INERTIA</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="3" t="n"/>
-      <c r="K41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>EMER_BUTTON</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="n"/>
-      <c r="J42" s="3" t="n"/>
-      <c r="K42" s="3" t="inlineStr"/>
-    </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT7</t>
-        </is>
-      </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x770</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board7</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>BRK_PRESS</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="3" t="n"/>
-      <c r="I46" s="3" t="n"/>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
-    </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_IGN_R2D</t>
-        </is>
-      </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x600</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>ignition_manual</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C50" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="3" t="n"/>
-      <c r="I50" s="3" t="n"/>
-      <c r="J50" s="3" t="n"/>
-      <c r="K50" s="3" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>r2d_manual</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C51" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="3" t="n"/>
-      <c r="I51" s="3" t="n"/>
-      <c r="J51" s="3" t="n"/>
-      <c r="K51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>ignition_auto</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3" t="n"/>
-      <c r="I52" s="3" t="n"/>
-      <c r="J52" s="3" t="n"/>
-      <c r="K52" s="3" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>r2d_auto</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="3" t="n"/>
-      <c r="I53" s="3" t="n"/>
-      <c r="J53" s="3" t="n"/>
-      <c r="K53" s="3" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>shutdown_signal</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="3" t="n"/>
-      <c r="I54" s="3" t="n"/>
-      <c r="J54" s="3" t="n"/>
-      <c r="K54" s="3" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>vcu_state</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="3" t="n"/>
-      <c r="I55" s="3" t="n"/>
-      <c r="J55" s="3" t="n"/>
-      <c r="K55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>R2D_button_raw</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C56" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="3" t="n"/>
-      <c r="I56" s="3" t="n"/>
-      <c r="J56" s="3" t="n"/>
-      <c r="K56" s="3" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>Ignition_switch_raw</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C57" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3" t="n"/>
-      <c r="I57" s="3" t="n"/>
-      <c r="J57" s="3" t="n"/>
-      <c r="K57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58"/>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_HV</t>
-        </is>
-      </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x81</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>HV</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="3" t="n"/>
-      <c r="I61" s="3" t="n"/>
-      <c r="J61" s="3" t="n"/>
-      <c r="K61" s="3" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>Brake_pressure_Front</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C62" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3" t="n"/>
-      <c r="I62" s="3" t="n"/>
-      <c r="J62" s="3" t="n"/>
-      <c r="K62" s="3" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>Brake_pressure_Rear</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="3" t="n"/>
-      <c r="I63" s="3" t="n"/>
-      <c r="J63" s="3" t="n"/>
-      <c r="K63" s="3" t="inlineStr"/>
-    </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_RPM</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x509</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>rpm_actual</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C67" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>6000</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr"/>
-    </row>
-    <row r="68"/>
-    <row r="69">
-      <c r="A69" s="1" t="inlineStr">
-        <is>
-          <t>Message: JETSON</t>
-        </is>
-      </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x61</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>AS_STATE</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J71" s="3" t="n"/>
-      <c r="K71" s="3" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>AS_MISSION</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C72" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F72" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J72" s="3" t="n"/>
-      <c r="K72" s="3" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>TEMPERATURE</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C73" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J73" s="3" t="n"/>
-      <c r="K73" s="3" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C74" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J74" s="3" t="n"/>
-      <c r="K74" s="3" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>GPU</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C75" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J75" s="3" t="n"/>
-      <c r="K75" s="3" t="inlineStr"/>
-    </row>
-    <row r="76"/>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr">
-        <is>
-          <t>Message: RES</t>
-        </is>
-      </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x191</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>SIGNAL</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F79" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="3" t="n"/>
-      <c r="I79" s="3" t="n"/>
-      <c r="J79" s="3" t="n"/>
-      <c r="K79" s="3" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="autonomous_t26" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="powertrain_t26" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="data_t26" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="aquisition_boards" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="powertrain_t26" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="data_t26" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="aquisition_boards" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="autonomous_t26" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,2410 +440,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="129" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Message: ACU</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x51</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ACU</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>IGN</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>0=OFF, 1=ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>ASMS</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>0=OFF, 1=ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>EMERGENCY</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>0=OFF, 1=ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>AS_STATE</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>1=OFF, 2=READY, 3=DRIVING, 4=EMERGENCY, 5=FINISH</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Mission_select</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>ACU_STATE</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>0=INIT, 1=MISSION_SELECT, 2=JETSON_WAITING, 3=INIT_SEQUENCE, 4=READY, 5=DRIVING, 6=EBS_ERROR, 7=EMERGENCY, 8=FINISHED, 9=MANUAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>ASSI_STATE</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>1=OFF, 2=READY, 3=DRIVING, 4=EMERGENCY, 5=FINISH</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>ACU_CPU_TEMP</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Message: CubeMars_Feedback</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x2968</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>-3200</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>3200</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Speed_RPM</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>1890</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>-320000</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>320000</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>ERPM</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>-60</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Driver_Temp</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>degC</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Error_Code</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Message: CubeMars_possition_loop</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x468</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): JETSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>POSITION</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT1</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x710</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board1</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>BRK_PRESS</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="3" t="n"/>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>RES</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>BOTS</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
-      <c r="J28" s="3" t="n"/>
-      <c r="K28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT2</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x720</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>WHEEL_ANGLE</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3" t="n"/>
-      <c r="I32" s="3" t="n"/>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr"/>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT3</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x730</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board3</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>WHEEL_ANGLE</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="3" t="n"/>
-      <c r="I36" s="3" t="n"/>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr"/>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT4</t>
-        </is>
-      </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x740</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board4</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>ST_ANGLE</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="n"/>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>INERTIA</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="3" t="n"/>
-      <c r="K41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>EMER_BUTTON</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="n"/>
-      <c r="J42" s="3" t="n"/>
-      <c r="K42" s="3" t="inlineStr"/>
-    </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT7</t>
-        </is>
-      </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x770</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board7</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>BRK_PRESS</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="3" t="n"/>
-      <c r="I46" s="3" t="n"/>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
-    </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_IGN_R2D</t>
-        </is>
-      </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x600</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>ignition_manual</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C50" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="3" t="n"/>
-      <c r="I50" s="3" t="n"/>
-      <c r="J50" s="3" t="n"/>
-      <c r="K50" s="3" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>r2d_manual</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C51" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="3" t="n"/>
-      <c r="I51" s="3" t="n"/>
-      <c r="J51" s="3" t="n"/>
-      <c r="K51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>ignition_auto</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3" t="n"/>
-      <c r="I52" s="3" t="n"/>
-      <c r="J52" s="3" t="n"/>
-      <c r="K52" s="3" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>r2d_auto</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="3" t="n"/>
-      <c r="I53" s="3" t="n"/>
-      <c r="J53" s="3" t="n"/>
-      <c r="K53" s="3" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>shutdown_signal</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="3" t="n"/>
-      <c r="I54" s="3" t="n"/>
-      <c r="J54" s="3" t="n"/>
-      <c r="K54" s="3" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>vcu_state</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="3" t="n"/>
-      <c r="I55" s="3" t="n"/>
-      <c r="J55" s="3" t="n"/>
-      <c r="K55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>R2D_button_raw</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C56" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="3" t="n"/>
-      <c r="I56" s="3" t="n"/>
-      <c r="J56" s="3" t="n"/>
-      <c r="K56" s="3" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>Ignition_switch_raw</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C57" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3" t="n"/>
-      <c r="I57" s="3" t="n"/>
-      <c r="J57" s="3" t="n"/>
-      <c r="K57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58"/>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_HV</t>
-        </is>
-      </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x81</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>HV</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="3" t="n"/>
-      <c r="I61" s="3" t="n"/>
-      <c r="J61" s="3" t="n"/>
-      <c r="K61" s="3" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>Brake_pressure_Front</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C62" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3" t="n"/>
-      <c r="I62" s="3" t="n"/>
-      <c r="J62" s="3" t="n"/>
-      <c r="K62" s="3" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>Brake_pressure_Rear</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="3" t="n"/>
-      <c r="I63" s="3" t="n"/>
-      <c r="J63" s="3" t="n"/>
-      <c r="K63" s="3" t="inlineStr"/>
-    </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_RPM</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x509</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>rpm_actual</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C67" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>6000</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr"/>
-    </row>
-    <row r="68"/>
-    <row r="69">
-      <c r="A69" s="1" t="inlineStr">
-        <is>
-          <t>Message: JETSON</t>
-        </is>
-      </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x61</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>AS_STATE</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J71" s="3" t="n"/>
-      <c r="K71" s="3" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>AS_MISSION</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C72" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F72" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J72" s="3" t="n"/>
-      <c r="K72" s="3" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>TEMPERATURE</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C73" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J73" s="3" t="n"/>
-      <c r="K73" s="3" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C74" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J74" s="3" t="n"/>
-      <c r="K74" s="3" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>GPU</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C75" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J75" s="3" t="n"/>
-      <c r="K75" s="3" t="inlineStr"/>
-    </row>
-    <row r="76"/>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr">
-        <is>
-          <t>Message: RES</t>
-        </is>
-      </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x191</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>SIGNAL</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F79" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="3" t="n"/>
-      <c r="I79" s="3" t="n"/>
-      <c r="J79" s="3" t="n"/>
-      <c r="K79" s="3" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:K1056"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -35641,7 +33237,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36712,7 +34308,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38088,4 +35684,3596 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K115"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="157" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Message: ACU</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x51</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ACU</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>ASSI_STATE</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>1=OFF, 2=READY, 3=DRIVING, 4=EMERGENCY, 5=FINISH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ACU_STATE</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>0=INIT, 1=MISSION_SELECT, 2=JETSON_WAITING, 3=INIT_SEQUENCE, 4=READY, 5=DRIVING, 6=EBS_ERROR, 7=EMERGENCY, 8=FINISHED, 9=MANUAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ACU_CPU_TEMP</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Mission_select</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>AS_STATE</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>1=OFF, 2=READY, 3=DRIVING, 4=EMERGENCY, 5=FINISH</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>EMERGENCY</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>0=OFF, 1=ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>ASMS</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>0=OFF, 1=ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>IGN</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>0=OFF, 1=ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>EMERGENCY_cause</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>0=None, 1=SDC_OPEN, 2=RES, 3=Pressure_checks, 4=VCU_timeout, 5=Jetson_timeout, 6=ACU_WDT_TRIGGERED, 7=dir_actuator_timeout, 8=CAN_Dynamics_Pressure_timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Message: CubeMars_Feedback</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x2968</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>-3200</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Speed_RPM</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1890</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>-320000</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>320000</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>ERPM</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Driver_Temp</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Error_Code</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Message: CubeMars_possition_loop</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x468</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>POSITION</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT1</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x710</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>BRK_PRESS</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>BOTS</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT2</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x720</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>WHEEL_ANGLE</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT3</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x730</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>WHEEL_ANGLE</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT4</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x740</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>ST_ANGLE</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>INERTIA</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3" t="n"/>
+      <c r="I42" s="3" t="n"/>
+      <c r="J42" s="3" t="n"/>
+      <c r="K42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>EMER_BUTTON</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" s="3" t="n"/>
+      <c r="K43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT7</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x770</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>BRK_PRESS</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_IGN_R2D</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x600</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>ignition_manual</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" s="3" t="n"/>
+      <c r="J51" s="3" t="n"/>
+      <c r="K51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>r2d_manual</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="n"/>
+      <c r="I52" s="3" t="n"/>
+      <c r="J52" s="3" t="n"/>
+      <c r="K52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>ignition_auto</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3" t="n"/>
+      <c r="I53" s="3" t="n"/>
+      <c r="J53" s="3" t="n"/>
+      <c r="K53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>r2d_auto</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3" t="n"/>
+      <c r="I54" s="3" t="n"/>
+      <c r="J54" s="3" t="n"/>
+      <c r="K54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>shutdown_signal</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3" t="n"/>
+      <c r="I55" s="3" t="n"/>
+      <c r="J55" s="3" t="n"/>
+      <c r="K55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>vcu_state</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3" t="n"/>
+      <c r="I56" s="3" t="n"/>
+      <c r="J56" s="3" t="n"/>
+      <c r="K56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>R2D_button_raw</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3" t="n"/>
+      <c r="I57" s="3" t="n"/>
+      <c r="J57" s="3" t="n"/>
+      <c r="K57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Ignition_switch_raw</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3" t="n"/>
+      <c r="I58" s="3" t="n"/>
+      <c r="J58" s="3" t="n"/>
+      <c r="K58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>Message: DV_dynamics_1</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x500</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ACU</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Speed_actual</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Speed_target</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Steering_angle_actual</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>-64</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Steering_angle_target</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>-64</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Brake_hydr_actual</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Brake_hydr_target</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Motor_moment_actual</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>-128</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Motor_moment_target</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>-128</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70"/>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>Message: DV_dynamics_2</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x501</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ACU</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Acceleration_longitudinal</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0.001953125</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="3" t="n"/>
+      <c r="I73" s="3" t="n"/>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>m/s2</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Acceleration_lateral</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>0.001953125</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="3" t="n"/>
+      <c r="I74" s="3" t="n"/>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>m/s2</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Yaw_rate</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0.0078125</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="3" t="n"/>
+      <c r="I75" s="3" t="n"/>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½/s</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76"/>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_HV</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x81</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="3" t="n"/>
+      <c r="I79" s="3" t="n"/>
+      <c r="J79" s="3" t="n"/>
+      <c r="K79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Brake_pressure_Front</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="3" t="n"/>
+      <c r="I80" s="3" t="n"/>
+      <c r="J80" s="3" t="n"/>
+      <c r="K80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Brake_pressure_Rear</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3" t="n"/>
+      <c r="I81" s="3" t="n"/>
+      <c r="J81" s="3" t="n"/>
+      <c r="K81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82"/>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>Message: DV_status</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x502</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ACU</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>AS_status</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J85" s="3" t="n"/>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>1=AS_status_off, 2=AS_status_ready, 3=AS_status_driving, 4=AS_status_emergency, 5=AS_status_finished</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>ASB_EBS_state</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J86" s="3" t="n"/>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>1=ASB_EBS_state_deactivated, 2=ASB_EBS_state_initial_checkup_passed, 3=ASB_EBS_state_activated</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>AMI_state</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J87" s="3" t="n"/>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>1=AMI_state_acceleration, 2=AMI_state_skidpad, 3=AMI_state_trackdrive, 4=AMI_state_braketest, 5=AMI_state_inspection, 6=AMI_state_autocross</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>Steering_state</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" s="3" t="n"/>
+      <c r="K88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>ASB_redundancy_state</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3" t="n"/>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>1=ASB_redundancy_state_deactivated, 2=ASB_redundancy_state_engaged, 3=ASB_redundancy_state_initial_checkup_passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>Lap_counter</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J90" s="3" t="n"/>
+      <c r="K90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Cones_count_actual</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J91" s="3" t="n"/>
+      <c r="K91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Cones_count_all</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>131071</v>
+      </c>
+      <c r="J92" s="3" t="n"/>
+      <c r="K92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93"/>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>Message: ASF_SIGNALS</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x511</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ACU</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>EBS_Pressure_Tank_Front</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3" t="n"/>
+      <c r="I96" s="3" t="n"/>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>EBS_Pressure_Tank_Rear</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="3" t="n"/>
+      <c r="I97" s="3" t="n"/>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>Brake_Pressure_Front</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="3" t="n"/>
+      <c r="I98" s="3" t="n"/>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Brake_Pressure_Rear</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="3" t="n"/>
+      <c r="I99" s="3" t="n"/>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_RPM</t>
+        </is>
+      </c>
+      <c r="B101" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x509</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>rpm_actual</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104"/>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>Message: JETSON</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x61</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>AS_STATE</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J107" s="3" t="n"/>
+      <c r="K107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>AS_MISSION</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J108" s="3" t="n"/>
+      <c r="K108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>TEMPERATURE</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J109" s="3" t="n"/>
+      <c r="K109" s="3" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J110" s="3" t="n"/>
+      <c r="K110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J111" s="3" t="n"/>
+      <c r="K111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112"/>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>Message: RES</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x191</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>SIGNAL</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="3" t="n"/>
+      <c r="I115" s="3" t="n"/>
+      <c r="J115" s="3" t="n"/>
+      <c r="K115" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="autonomous_t26" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="powertrain_t26" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="data_t26" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="aquisition_boards" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="powertrain_t26" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="data_t26" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="aquisition_boards" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="autonomous_t26" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,3598 +440,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K115"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="157" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Message: ACU</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x51</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ACU</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>ASSI_STATE</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>1=OFF, 2=READY, 3=DRIVING, 4=EMERGENCY, 5=FINISH</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>ACU_STATE</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>0=INIT, 1=MISSION_SELECT, 2=JETSON_WAITING, 3=INIT_SEQUENCE, 4=READY, 5=DRIVING, 6=EBS_ERROR, 7=EMERGENCY, 8=FINISHED, 9=MANUAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>ACU_CPU_TEMP</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Mission_select</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>AS_STATE</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>1=OFF, 2=READY, 3=DRIVING, 4=EMERGENCY, 5=FINISH</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>EMERGENCY</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>0=OFF, 1=ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>ASMS</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>0=OFF, 1=ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>IGN</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>0=OFF, 1=ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>EMERGENCY_cause</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>0=None, 1=SDC_OPEN, 2=RES, 3=Pressure_checks, 4=VCU_timeout, 5=Jetson_timeout, 6=ACU_WDT_TRIGGERED, 7=dir_actuator_timeout, 8=CAN_Dynamics_Pressure_timeout</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Message: CubeMars_Feedback</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x2968</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>-3200</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>3200</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Speed_RPM</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>1890</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>-320000</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>320000</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>ERPM</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>-60</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Driver_Temp</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>degC</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Error_Code</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>Message: CubeMars_possition_loop</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x468</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): JETSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>POSITION</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT1</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x710</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>BRK_PRESS</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>RES</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
-      <c r="J28" s="3" t="n"/>
-      <c r="K28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>BOTS</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n"/>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT2</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x720</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board2</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>WHEEL_ANGLE</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="n"/>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT3</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x730</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board3</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>WHEEL_ANGLE</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="3" t="n"/>
-      <c r="I37" s="3" t="n"/>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT4</t>
-        </is>
-      </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x740</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board4</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>ST_ANGLE</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>INERTIA</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="n"/>
-      <c r="J42" s="3" t="n"/>
-      <c r="K42" s="3" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>EMER_BUTTON</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3" t="n"/>
-      <c r="I43" s="3" t="n"/>
-      <c r="J43" s="3" t="n"/>
-      <c r="K43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT7</t>
-        </is>
-      </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x770</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board7</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>BRK_PRESS</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3" t="n"/>
-      <c r="I47" s="3" t="n"/>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_IGN_R2D</t>
-        </is>
-      </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x600</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>ignition_manual</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="3" t="n"/>
-      <c r="I51" s="3" t="n"/>
-      <c r="J51" s="3" t="n"/>
-      <c r="K51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>r2d_manual</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3" t="n"/>
-      <c r="I52" s="3" t="n"/>
-      <c r="J52" s="3" t="n"/>
-      <c r="K52" s="3" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>ignition_auto</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="3" t="n"/>
-      <c r="I53" s="3" t="n"/>
-      <c r="J53" s="3" t="n"/>
-      <c r="K53" s="3" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>r2d_auto</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="3" t="n"/>
-      <c r="I54" s="3" t="n"/>
-      <c r="J54" s="3" t="n"/>
-      <c r="K54" s="3" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>shutdown_signal</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="3" t="n"/>
-      <c r="I55" s="3" t="n"/>
-      <c r="J55" s="3" t="n"/>
-      <c r="K55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>vcu_state</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="C56" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="3" t="n"/>
-      <c r="I56" s="3" t="n"/>
-      <c r="J56" s="3" t="n"/>
-      <c r="K56" s="3" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>R2D_button_raw</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C57" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3" t="n"/>
-      <c r="I57" s="3" t="n"/>
-      <c r="J57" s="3" t="n"/>
-      <c r="K57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Ignition_switch_raw</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C58" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3" t="n"/>
-      <c r="I58" s="3" t="n"/>
-      <c r="J58" s="3" t="n"/>
-      <c r="K58" s="3" t="inlineStr"/>
-    </row>
-    <row r="59"/>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>Message: DV_dynamics_1</t>
-        </is>
-      </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x500</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ACU</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>Speed_actual</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>km/h</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>Speed_target</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>km/h</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>Steering_angle_actual</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C64" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>-64</v>
-      </c>
-      <c r="I64" s="3" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>Steering_angle_target</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C65" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="3" t="n">
-        <v>-64</v>
-      </c>
-      <c r="I65" s="3" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K65" s="3" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>Brake_hydr_actual</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C66" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>Brake_hydr_target</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="C67" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>Motor_moment_actual</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C68" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="3" t="n">
-        <v>-128</v>
-      </c>
-      <c r="I68" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="K68" s="3" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>Motor_moment_target</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C69" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="3" t="n">
-        <v>-128</v>
-      </c>
-      <c r="I69" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="inlineStr"/>
-    </row>
-    <row r="70"/>
-    <row r="71">
-      <c r="A71" s="1" t="inlineStr">
-        <is>
-          <t>Message: DV_dynamics_2</t>
-        </is>
-      </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x501</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ACU</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>Acceleration_longitudinal</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C73" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>0.001953125</v>
-      </c>
-      <c r="G73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="3" t="n"/>
-      <c r="I73" s="3" t="n"/>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>m/s2</t>
-        </is>
-      </c>
-      <c r="K73" s="3" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>Acceleration_lateral</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C74" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>0.001953125</v>
-      </c>
-      <c r="G74" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="3" t="n"/>
-      <c r="I74" s="3" t="n"/>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>m/s2</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>Yaw_rate</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C75" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>0.0078125</v>
-      </c>
-      <c r="G75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="3" t="n"/>
-      <c r="I75" s="3" t="n"/>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½/s</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="inlineStr"/>
-    </row>
-    <row r="76"/>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_HV</t>
-        </is>
-      </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x81</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>HV</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F79" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="3" t="n"/>
-      <c r="I79" s="3" t="n"/>
-      <c r="J79" s="3" t="n"/>
-      <c r="K79" s="3" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>Brake_pressure_Front</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C80" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F80" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="3" t="n"/>
-      <c r="I80" s="3" t="n"/>
-      <c r="J80" s="3" t="n"/>
-      <c r="K80" s="3" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>Brake_pressure_Rear</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C81" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F81" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="3" t="n"/>
-      <c r="I81" s="3" t="n"/>
-      <c r="J81" s="3" t="n"/>
-      <c r="K81" s="3" t="inlineStr"/>
-    </row>
-    <row r="82"/>
-    <row r="83">
-      <c r="A83" s="1" t="inlineStr">
-        <is>
-          <t>Message: DV_status</t>
-        </is>
-      </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x502</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ACU</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>AS_status</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J85" s="3" t="n"/>
-      <c r="K85" s="3" t="inlineStr">
-        <is>
-          <t>1=AS_status_off, 2=AS_status_ready, 3=AS_status_driving, 4=AS_status_emergency, 5=AS_status_finished</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>ASB_EBS_state</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C86" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J86" s="3" t="n"/>
-      <c r="K86" s="3" t="inlineStr">
-        <is>
-          <t>1=ASB_EBS_state_deactivated, 2=ASB_EBS_state_initial_checkup_passed, 3=ASB_EBS_state_activated</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>AMI_state</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C87" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J87" s="3" t="n"/>
-      <c r="K87" s="3" t="inlineStr">
-        <is>
-          <t>1=AMI_state_acceleration, 2=AMI_state_skidpad, 3=AMI_state_trackdrive, 4=AMI_state_braketest, 5=AMI_state_inspection, 6=AMI_state_autocross</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>Steering_state</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C88" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="3" t="n"/>
-      <c r="K88" s="3" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>ASB_redundancy_state</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C89" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="n"/>
-      <c r="K89" s="3" t="inlineStr">
-        <is>
-          <t>1=ASB_redundancy_state_deactivated, 2=ASB_redundancy_state_engaged, 3=ASB_redundancy_state_initial_checkup_passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>Lap_counter</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="C90" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J90" s="3" t="n"/>
-      <c r="K90" s="3" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>Cones_count_actual</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C91" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J91" s="3" t="n"/>
-      <c r="K91" s="3" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>Cones_count_all</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C92" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="3" t="n">
-        <v>131071</v>
-      </c>
-      <c r="J92" s="3" t="n"/>
-      <c r="K92" s="3" t="inlineStr"/>
-    </row>
-    <row r="93"/>
-    <row r="94">
-      <c r="A94" s="1" t="inlineStr">
-        <is>
-          <t>Message: ASF_SIGNALS</t>
-        </is>
-      </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x511</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ACU</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>EBS_Pressure_Tank_Front</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C96" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3" t="n"/>
-      <c r="I96" s="3" t="n"/>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K96" s="3" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>EBS_Pressure_Tank_Rear</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C97" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F97" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="3" t="n"/>
-      <c r="I97" s="3" t="n"/>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K97" s="3" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>Brake_Pressure_Front</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C98" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F98" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="3" t="n"/>
-      <c r="I98" s="3" t="n"/>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K98" s="3" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>Brake_Pressure_Rear</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C99" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F99" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" s="3" t="n"/>
-      <c r="I99" s="3" t="n"/>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K99" s="3" t="inlineStr"/>
-    </row>
-    <row r="100"/>
-    <row r="101">
-      <c r="A101" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_RPM</t>
-        </is>
-      </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x509</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>rpm_actual</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C103" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F103" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" s="3" t="n">
-        <v>6000</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
-      <c r="K103" s="3" t="inlineStr"/>
-    </row>
-    <row r="104"/>
-    <row r="105">
-      <c r="A105" s="1" t="inlineStr">
-        <is>
-          <t>Message: JETSON</t>
-        </is>
-      </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x61</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>AS_STATE</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C107" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F107" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J107" s="3" t="n"/>
-      <c r="K107" s="3" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>AS_MISSION</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C108" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F108" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J108" s="3" t="n"/>
-      <c r="K108" s="3" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>TEMPERATURE</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C109" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F109" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G109" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J109" s="3" t="n"/>
-      <c r="K109" s="3" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C110" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F110" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J110" s="3" t="n"/>
-      <c r="K110" s="3" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>GPU</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C111" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F111" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G111" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H111" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J111" s="3" t="n"/>
-      <c r="K111" s="3" t="inlineStr"/>
-    </row>
-    <row r="112"/>
-    <row r="113">
-      <c r="A113" s="1" t="inlineStr">
-        <is>
-          <t>Message: RES</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x191</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>SIGNAL</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C115" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F115" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G115" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" s="3" t="n"/>
-      <c r="I115" s="3" t="n"/>
-      <c r="J115" s="3" t="n"/>
-      <c r="K115" s="3" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:K1068"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -37199,7 +33607,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38270,7 +34678,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -39646,4 +36054,3596 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K115"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="157" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Message: ACU</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x51</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ACU</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>ASSI_STATE</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>1=OFF, 2=READY, 3=DRIVING, 4=EMERGENCY, 5=FINISH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ACU_STATE</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>0=INIT, 1=MISSION_SELECT, 2=JETSON_WAITING, 3=INIT_SEQUENCE, 4=READY, 5=DRIVING, 6=EBS_ERROR, 7=EMERGENCY, 8=FINISHED, 9=MANUAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ACU_CPU_TEMP</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Mission_select</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>AS_STATE</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>1=OFF, 2=READY, 3=DRIVING, 4=EMERGENCY, 5=FINISH</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>EMERGENCY</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>0=OFF, 1=ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>ASMS</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>0=OFF, 1=ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>IGN</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>0=OFF, 1=ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>EMERGENCY_cause</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>0=None, 1=SDC_OPEN, 2=RES, 3=Pressure_checks, 4=VCU_timeout, 5=Jetson_timeout, 6=ACU_WDT_TRIGGERED, 7=dir_actuator_timeout, 8=CAN_Dynamics_Pressure_timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Message: CubeMars_Feedback</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x2968</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>-3200</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Speed_RPM</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1890</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>-320000</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>320000</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>ERPM</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Driver_Temp</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Error_Code</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Message: CubeMars_possition_loop</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x468</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>POSITION</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT1</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x710</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>BRK_PRESS</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>BOTS</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT2</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x720</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>WHEEL_ANGLE</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT3</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x730</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>WHEEL_ANGLE</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT4</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x740</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>ST_ANGLE</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>INERTIA</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3" t="n"/>
+      <c r="I42" s="3" t="n"/>
+      <c r="J42" s="3" t="n"/>
+      <c r="K42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>EMER_BUTTON</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" s="3" t="n"/>
+      <c r="K43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT7</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x770</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>BRK_PRESS</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_IGN_R2D</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x600</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>ignition_manual</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" s="3" t="n"/>
+      <c r="J51" s="3" t="n"/>
+      <c r="K51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>r2d_manual</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="n"/>
+      <c r="I52" s="3" t="n"/>
+      <c r="J52" s="3" t="n"/>
+      <c r="K52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>ignition_auto</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3" t="n"/>
+      <c r="I53" s="3" t="n"/>
+      <c r="J53" s="3" t="n"/>
+      <c r="K53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>r2d_auto</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3" t="n"/>
+      <c r="I54" s="3" t="n"/>
+      <c r="J54" s="3" t="n"/>
+      <c r="K54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>shutdown_signal</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3" t="n"/>
+      <c r="I55" s="3" t="n"/>
+      <c r="J55" s="3" t="n"/>
+      <c r="K55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>vcu_state</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3" t="n"/>
+      <c r="I56" s="3" t="n"/>
+      <c r="J56" s="3" t="n"/>
+      <c r="K56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>R2D_button_raw</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3" t="n"/>
+      <c r="I57" s="3" t="n"/>
+      <c r="J57" s="3" t="n"/>
+      <c r="K57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Ignition_switch_raw</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3" t="n"/>
+      <c r="I58" s="3" t="n"/>
+      <c r="J58" s="3" t="n"/>
+      <c r="K58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>Message: DV_dynamics_1</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x500</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ACU</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Speed_actual</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Speed_target</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Steering_angle_actual</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>-64</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Steering_angle_target</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>-64</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Brake_hydr_actual</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Brake_hydr_target</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Motor_moment_actual</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>-128</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Motor_moment_target</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>-128</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70"/>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>Message: DV_dynamics_2</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x501</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ACU</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Acceleration_longitudinal</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0.001953125</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="3" t="n"/>
+      <c r="I73" s="3" t="n"/>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>m/s2</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Acceleration_lateral</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>0.001953125</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="3" t="n"/>
+      <c r="I74" s="3" t="n"/>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>m/s2</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Yaw_rate</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0.0078125</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="3" t="n"/>
+      <c r="I75" s="3" t="n"/>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½/s</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76"/>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_HV</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x81</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="3" t="n"/>
+      <c r="I79" s="3" t="n"/>
+      <c r="J79" s="3" t="n"/>
+      <c r="K79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Brake_pressure_Front</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="3" t="n"/>
+      <c r="I80" s="3" t="n"/>
+      <c r="J80" s="3" t="n"/>
+      <c r="K80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Brake_pressure_Rear</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3" t="n"/>
+      <c r="I81" s="3" t="n"/>
+      <c r="J81" s="3" t="n"/>
+      <c r="K81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82"/>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>Message: DV_status</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x502</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ACU</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>AS_status</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J85" s="3" t="n"/>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>1=AS_status_off, 2=AS_status_ready, 3=AS_status_driving, 4=AS_status_emergency, 5=AS_status_finished</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>ASB_EBS_state</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J86" s="3" t="n"/>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>1=ASB_EBS_state_deactivated, 2=ASB_EBS_state_initial_checkup_passed, 3=ASB_EBS_state_activated</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>AMI_state</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J87" s="3" t="n"/>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>1=AMI_state_acceleration, 2=AMI_state_skidpad, 3=AMI_state_trackdrive, 4=AMI_state_braketest, 5=AMI_state_inspection, 6=AMI_state_autocross</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>Steering_state</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" s="3" t="n"/>
+      <c r="K88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>ASB_redundancy_state</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3" t="n"/>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>1=ASB_redundancy_state_deactivated, 2=ASB_redundancy_state_engaged, 3=ASB_redundancy_state_initial_checkup_passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>Lap_counter</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J90" s="3" t="n"/>
+      <c r="K90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Cones_count_actual</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J91" s="3" t="n"/>
+      <c r="K91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Cones_count_all</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>131071</v>
+      </c>
+      <c r="J92" s="3" t="n"/>
+      <c r="K92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93"/>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>Message: ASF_SIGNALS</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x511</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ACU</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>EBS_Pressure_Tank_Front</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3" t="n"/>
+      <c r="I96" s="3" t="n"/>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>EBS_Pressure_Tank_Rear</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="3" t="n"/>
+      <c r="I97" s="3" t="n"/>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>Brake_Pressure_Front</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="3" t="n"/>
+      <c r="I98" s="3" t="n"/>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Brake_Pressure_Rear</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="3" t="n"/>
+      <c r="I99" s="3" t="n"/>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_RPM</t>
+        </is>
+      </c>
+      <c r="B101" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x509</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>rpm_actual</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104"/>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>Message: JETSON</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x61</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>AS_STATE</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J107" s="3" t="n"/>
+      <c r="K107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>AS_MISSION</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J108" s="3" t="n"/>
+      <c r="K108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>TEMPERATURE</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J109" s="3" t="n"/>
+      <c r="K109" s="3" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J110" s="3" t="n"/>
+      <c r="K110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J111" s="3" t="n"/>
+      <c r="K111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112"/>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>Message: RES</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x191</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>SIGNAL</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="3" t="n"/>
+      <c r="I115" s="3" t="n"/>
+      <c r="J115" s="3" t="n"/>
+      <c r="K115" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -19467,7 +19467,7 @@
         <v>8</v>
       </c>
       <c r="C616" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D616" s="3" t="inlineStr">
         <is>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="powertrain_t26" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="data_t26" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="aquisition_boards" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="autonomous_t26" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="autonomous_t26" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="powertrain_t26" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="data_t26" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="aquisition_boards" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,6 +440,3826 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K123"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="157" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Message: ACU</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x51</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ACU</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>ASSI_STATE</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>1=OFF, 2=READY, 3=DRIVING, 4=EMERGENCY, 5=FINISH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ACU_STATE</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>0=INIT, 1=MISSION_SELECT, 2=JETSON_WAITING, 3=INIT_SEQUENCE, 4=READY, 5=DRIVING, 6=EBS_ERROR, 7=EMERGENCY, 8=FINISHED, 9=MANUAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ACU_CPU_TEMP</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Mission_select</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>AS_STATE</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>1=OFF, 2=READY, 3=DRIVING, 4=EMERGENCY, 5=FINISH</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>EMERGENCY</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>0=OFF, 1=ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>ASMS</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>0=OFF, 1=ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>IGN</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>0=OFF, 1=ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>EMERGENCY_cause</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>0=None, 1=SDC_OPEN, 2=RES, 3=Pressure_checks, 4=VCU_timeout, 5=Jetson_timeout, 6=ACU_WDT_TRIGGERED, 7=dir_actuator_timeout, 8=CAN_Dynamics_Pressure_timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Message: CubeMars_Feedback</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x2968</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>-3200</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Speed_RPM</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1890</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>-320000</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>320000</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>ERPM</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Driver_Temp</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Error_Code</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Message: CubeMars_possition_loop</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x468</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>POSITION</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT1</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x710</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>BRK_PRESS</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>BOTS</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT2</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x720</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>WHEEL_ANGLE</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT3</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x730</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>WHEEL_ANGLE</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT4</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x740</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>ST_ANGLE</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>INERTIA</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3" t="n"/>
+      <c r="I42" s="3" t="n"/>
+      <c r="J42" s="3" t="n"/>
+      <c r="K42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>EMER_BUTTON</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" s="3" t="n"/>
+      <c r="K43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT7</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x770</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>BRK_PRESS</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_IGN_R2D</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x600</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>ignition_manual</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" s="3" t="n"/>
+      <c r="J51" s="3" t="n"/>
+      <c r="K51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>r2d_manual</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="n"/>
+      <c r="I52" s="3" t="n"/>
+      <c r="J52" s="3" t="n"/>
+      <c r="K52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>ignition_auto</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3" t="n"/>
+      <c r="I53" s="3" t="n"/>
+      <c r="J53" s="3" t="n"/>
+      <c r="K53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>r2d_auto</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3" t="n"/>
+      <c r="I54" s="3" t="n"/>
+      <c r="J54" s="3" t="n"/>
+      <c r="K54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>shutdown_signal</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3" t="n"/>
+      <c r="I55" s="3" t="n"/>
+      <c r="J55" s="3" t="n"/>
+      <c r="K55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>vcu_state</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3" t="n"/>
+      <c r="I56" s="3" t="n"/>
+      <c r="J56" s="3" t="n"/>
+      <c r="K56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>R2D_button_raw</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3" t="n"/>
+      <c r="I57" s="3" t="n"/>
+      <c r="J57" s="3" t="n"/>
+      <c r="K57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Ignition_switch_raw</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3" t="n"/>
+      <c r="I58" s="3" t="n"/>
+      <c r="J58" s="3" t="n"/>
+      <c r="K58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>Message: DV_dynamics_1</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x500</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ACU</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Speed_actual</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Speed_target</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Steering_angle_actual</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>-64</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Steering_angle_target</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>-64</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Brake_hydr_actual</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Brake_hydr_target</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Motor_moment_actual</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>-128</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Motor_moment_target</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>-128</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70"/>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>Message: DV_dynamics_2</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x501</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ACU</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Acceleration_longitudinal</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0.001953125</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="3" t="n"/>
+      <c r="I73" s="3" t="n"/>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>m/s2</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Acceleration_lateral</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>0.001953125</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="3" t="n"/>
+      <c r="I74" s="3" t="n"/>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>m/s2</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Yaw_rate</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0.0078125</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="3" t="n"/>
+      <c r="I75" s="3" t="n"/>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½/s</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76"/>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_HV</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x81</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="3" t="n"/>
+      <c r="I79" s="3" t="n"/>
+      <c r="J79" s="3" t="n"/>
+      <c r="K79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Brake_pressure_Front</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="3" t="n"/>
+      <c r="I80" s="3" t="n"/>
+      <c r="J80" s="3" t="n"/>
+      <c r="K80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Brake_pressure_Rear</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3" t="n"/>
+      <c r="I81" s="3" t="n"/>
+      <c r="J81" s="3" t="n"/>
+      <c r="K81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82"/>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>Message: DV_status</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x502</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ACU</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>AS_status</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J85" s="3" t="n"/>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>1=AS_status_off, 2=AS_status_ready, 3=AS_status_driving, 4=AS_status_emergency, 5=AS_status_finished</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>ASB_EBS_state</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J86" s="3" t="n"/>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>1=ASB_EBS_state_deactivated, 2=ASB_EBS_state_initial_checkup_passed, 3=ASB_EBS_state_activated</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>AMI_state</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J87" s="3" t="n"/>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>1=AMI_state_acceleration, 2=AMI_state_skidpad, 3=AMI_state_trackdrive, 4=AMI_state_braketest, 5=AMI_state_inspection, 6=AMI_state_autocross</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>Steering_state</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" s="3" t="n"/>
+      <c r="K88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>ASB_redundancy_state</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3" t="n"/>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>1=ASB_redundancy_state_deactivated, 2=ASB_redundancy_state_engaged, 3=ASB_redundancy_state_initial_checkup_passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>Lap_counter</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J90" s="3" t="n"/>
+      <c r="K90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Cones_count_actual</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J91" s="3" t="n"/>
+      <c r="K91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Cones_count_all</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>131071</v>
+      </c>
+      <c r="J92" s="3" t="n"/>
+      <c r="K92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93"/>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>Message: ASF_SIGNALS</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x511</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ACU</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>EBS_Pressure_Tank_Front</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3" t="n"/>
+      <c r="I96" s="3" t="n"/>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>EBS_Pressure_Tank_Rear</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="3" t="n"/>
+      <c r="I97" s="3" t="n"/>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>Brake_Pressure_Front</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="3" t="n"/>
+      <c r="I98" s="3" t="n"/>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Brake_Pressure_Rear</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="3" t="n"/>
+      <c r="I99" s="3" t="n"/>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_RPM</t>
+        </is>
+      </c>
+      <c r="B101" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x509</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>rpm_actual</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104"/>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_TORQUE_TARGET</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x49a</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>torque_target</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="3" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I107" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108"/>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_RPM_TARGET</t>
+        </is>
+      </c>
+      <c r="B109" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x499</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>rpm_target</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112"/>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>Message: JETSON</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x61</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>AS_STATE</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J115" s="3" t="n"/>
+      <c r="K115" s="3" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>AS_MISSION</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J116" s="3" t="n"/>
+      <c r="K116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>TEMPERATURE</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J117" s="3" t="n"/>
+      <c r="K117" s="3" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J118" s="3" t="n"/>
+      <c r="K118" s="3" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J119" s="3" t="n"/>
+      <c r="K119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120"/>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>Message: RES</t>
+        </is>
+      </c>
+      <c r="B121" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x191</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>SIGNAL</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="3" t="n"/>
+      <c r="I123" s="3" t="n"/>
+      <c r="J123" s="3" t="n"/>
+      <c r="K123" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K1068"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -33607,7 +37427,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34678,7 +38498,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36054,3596 +39874,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K115"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="157" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Message: ACU</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x51</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ACU</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>ASSI_STATE</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>1=OFF, 2=READY, 3=DRIVING, 4=EMERGENCY, 5=FINISH</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>ACU_STATE</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>0=INIT, 1=MISSION_SELECT, 2=JETSON_WAITING, 3=INIT_SEQUENCE, 4=READY, 5=DRIVING, 6=EBS_ERROR, 7=EMERGENCY, 8=FINISHED, 9=MANUAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>ACU_CPU_TEMP</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Mission_select</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>AS_STATE</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>1=OFF, 2=READY, 3=DRIVING, 4=EMERGENCY, 5=FINISH</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>EMERGENCY</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>0=OFF, 1=ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>ASMS</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>0=OFF, 1=ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>IGN</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>0=OFF, 1=ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>EMERGENCY_cause</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>0=None, 1=SDC_OPEN, 2=RES, 3=Pressure_checks, 4=VCU_timeout, 5=Jetson_timeout, 6=ACU_WDT_TRIGGERED, 7=dir_actuator_timeout, 8=CAN_Dynamics_Pressure_timeout</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Message: CubeMars_Feedback</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x2968</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>-3200</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>3200</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Speed_RPM</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>1890</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>-320000</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>320000</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>ERPM</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>-60</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Driver_Temp</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>degC</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Error_Code</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>Message: CubeMars_possition_loop</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x468</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): JETSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>POSITION</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT1</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x710</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>BRK_PRESS</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>RES</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
-      <c r="J28" s="3" t="n"/>
-      <c r="K28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>BOTS</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n"/>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT2</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x720</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board2</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>WHEEL_ANGLE</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="n"/>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT3</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x730</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board3</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>WHEEL_ANGLE</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="3" t="n"/>
-      <c r="I37" s="3" t="n"/>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT4</t>
-        </is>
-      </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x740</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board4</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>ST_ANGLE</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>INERTIA</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="n"/>
-      <c r="J42" s="3" t="n"/>
-      <c r="K42" s="3" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>EMER_BUTTON</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3" t="n"/>
-      <c r="I43" s="3" t="n"/>
-      <c r="J43" s="3" t="n"/>
-      <c r="K43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT7</t>
-        </is>
-      </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x770</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board7</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>BRK_PRESS</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3" t="n"/>
-      <c r="I47" s="3" t="n"/>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_IGN_R2D</t>
-        </is>
-      </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x600</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>ignition_manual</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="3" t="n"/>
-      <c r="I51" s="3" t="n"/>
-      <c r="J51" s="3" t="n"/>
-      <c r="K51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>r2d_manual</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3" t="n"/>
-      <c r="I52" s="3" t="n"/>
-      <c r="J52" s="3" t="n"/>
-      <c r="K52" s="3" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>ignition_auto</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="3" t="n"/>
-      <c r="I53" s="3" t="n"/>
-      <c r="J53" s="3" t="n"/>
-      <c r="K53" s="3" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>r2d_auto</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="3" t="n"/>
-      <c r="I54" s="3" t="n"/>
-      <c r="J54" s="3" t="n"/>
-      <c r="K54" s="3" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>shutdown_signal</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="3" t="n"/>
-      <c r="I55" s="3" t="n"/>
-      <c r="J55" s="3" t="n"/>
-      <c r="K55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>vcu_state</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="C56" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="3" t="n"/>
-      <c r="I56" s="3" t="n"/>
-      <c r="J56" s="3" t="n"/>
-      <c r="K56" s="3" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>R2D_button_raw</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C57" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3" t="n"/>
-      <c r="I57" s="3" t="n"/>
-      <c r="J57" s="3" t="n"/>
-      <c r="K57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Ignition_switch_raw</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C58" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3" t="n"/>
-      <c r="I58" s="3" t="n"/>
-      <c r="J58" s="3" t="n"/>
-      <c r="K58" s="3" t="inlineStr"/>
-    </row>
-    <row r="59"/>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>Message: DV_dynamics_1</t>
-        </is>
-      </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x500</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ACU</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>Speed_actual</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>km/h</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>Speed_target</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>km/h</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>Steering_angle_actual</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C64" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>-64</v>
-      </c>
-      <c r="I64" s="3" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>Steering_angle_target</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C65" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="3" t="n">
-        <v>-64</v>
-      </c>
-      <c r="I65" s="3" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K65" s="3" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>Brake_hydr_actual</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C66" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>Brake_hydr_target</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="C67" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>Motor_moment_actual</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C68" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="3" t="n">
-        <v>-128</v>
-      </c>
-      <c r="I68" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="K68" s="3" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>Motor_moment_target</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C69" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="3" t="n">
-        <v>-128</v>
-      </c>
-      <c r="I69" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="inlineStr"/>
-    </row>
-    <row r="70"/>
-    <row r="71">
-      <c r="A71" s="1" t="inlineStr">
-        <is>
-          <t>Message: DV_dynamics_2</t>
-        </is>
-      </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x501</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ACU</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>Acceleration_longitudinal</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C73" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>0.001953125</v>
-      </c>
-      <c r="G73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="3" t="n"/>
-      <c r="I73" s="3" t="n"/>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>m/s2</t>
-        </is>
-      </c>
-      <c r="K73" s="3" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>Acceleration_lateral</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C74" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>0.001953125</v>
-      </c>
-      <c r="G74" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="3" t="n"/>
-      <c r="I74" s="3" t="n"/>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>m/s2</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>Yaw_rate</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C75" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>0.0078125</v>
-      </c>
-      <c r="G75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="3" t="n"/>
-      <c r="I75" s="3" t="n"/>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½/s</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="inlineStr"/>
-    </row>
-    <row r="76"/>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_HV</t>
-        </is>
-      </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x81</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>HV</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F79" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="3" t="n"/>
-      <c r="I79" s="3" t="n"/>
-      <c r="J79" s="3" t="n"/>
-      <c r="K79" s="3" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>Brake_pressure_Front</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C80" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F80" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="3" t="n"/>
-      <c r="I80" s="3" t="n"/>
-      <c r="J80" s="3" t="n"/>
-      <c r="K80" s="3" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>Brake_pressure_Rear</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C81" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F81" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="3" t="n"/>
-      <c r="I81" s="3" t="n"/>
-      <c r="J81" s="3" t="n"/>
-      <c r="K81" s="3" t="inlineStr"/>
-    </row>
-    <row r="82"/>
-    <row r="83">
-      <c r="A83" s="1" t="inlineStr">
-        <is>
-          <t>Message: DV_status</t>
-        </is>
-      </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x502</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ACU</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>AS_status</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J85" s="3" t="n"/>
-      <c r="K85" s="3" t="inlineStr">
-        <is>
-          <t>1=AS_status_off, 2=AS_status_ready, 3=AS_status_driving, 4=AS_status_emergency, 5=AS_status_finished</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>ASB_EBS_state</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C86" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J86" s="3" t="n"/>
-      <c r="K86" s="3" t="inlineStr">
-        <is>
-          <t>1=ASB_EBS_state_deactivated, 2=ASB_EBS_state_initial_checkup_passed, 3=ASB_EBS_state_activated</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>AMI_state</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C87" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J87" s="3" t="n"/>
-      <c r="K87" s="3" t="inlineStr">
-        <is>
-          <t>1=AMI_state_acceleration, 2=AMI_state_skidpad, 3=AMI_state_trackdrive, 4=AMI_state_braketest, 5=AMI_state_inspection, 6=AMI_state_autocross</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>Steering_state</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C88" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="3" t="n"/>
-      <c r="K88" s="3" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>ASB_redundancy_state</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C89" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="n"/>
-      <c r="K89" s="3" t="inlineStr">
-        <is>
-          <t>1=ASB_redundancy_state_deactivated, 2=ASB_redundancy_state_engaged, 3=ASB_redundancy_state_initial_checkup_passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>Lap_counter</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="C90" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J90" s="3" t="n"/>
-      <c r="K90" s="3" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>Cones_count_actual</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C91" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J91" s="3" t="n"/>
-      <c r="K91" s="3" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>Cones_count_all</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C92" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="3" t="n">
-        <v>131071</v>
-      </c>
-      <c r="J92" s="3" t="n"/>
-      <c r="K92" s="3" t="inlineStr"/>
-    </row>
-    <row r="93"/>
-    <row r="94">
-      <c r="A94" s="1" t="inlineStr">
-        <is>
-          <t>Message: ASF_SIGNALS</t>
-        </is>
-      </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x511</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ACU</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>EBS_Pressure_Tank_Front</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C96" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3" t="n"/>
-      <c r="I96" s="3" t="n"/>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K96" s="3" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>EBS_Pressure_Tank_Rear</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C97" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F97" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="3" t="n"/>
-      <c r="I97" s="3" t="n"/>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K97" s="3" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>Brake_Pressure_Front</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C98" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F98" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="3" t="n"/>
-      <c r="I98" s="3" t="n"/>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K98" s="3" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>Brake_Pressure_Rear</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C99" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F99" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" s="3" t="n"/>
-      <c r="I99" s="3" t="n"/>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K99" s="3" t="inlineStr"/>
-    </row>
-    <row r="100"/>
-    <row r="101">
-      <c r="A101" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_RPM</t>
-        </is>
-      </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x509</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>rpm_actual</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C103" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F103" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" s="3" t="n">
-        <v>6000</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
-      <c r="K103" s="3" t="inlineStr"/>
-    </row>
-    <row r="104"/>
-    <row r="105">
-      <c r="A105" s="1" t="inlineStr">
-        <is>
-          <t>Message: JETSON</t>
-        </is>
-      </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x61</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>AS_STATE</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C107" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F107" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J107" s="3" t="n"/>
-      <c r="K107" s="3" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>AS_MISSION</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C108" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F108" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J108" s="3" t="n"/>
-      <c r="K108" s="3" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>TEMPERATURE</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C109" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F109" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G109" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J109" s="3" t="n"/>
-      <c r="K109" s="3" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C110" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F110" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J110" s="3" t="n"/>
-      <c r="K110" s="3" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>GPU</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C111" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F111" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G111" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H111" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J111" s="3" t="n"/>
-      <c r="K111" s="3" t="inlineStr"/>
-    </row>
-    <row r="112"/>
-    <row r="113">
-      <c r="A113" s="1" t="inlineStr">
-        <is>
-          <t>Message: RES</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x191</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>SIGNAL</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C115" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F115" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G115" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" s="3" t="n"/>
-      <c r="I115" s="3" t="n"/>
-      <c r="J115" s="3" t="n"/>
-      <c r="K115" s="3" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="autonomous_t26" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="powertrain_t26" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="data_t26" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="aquisition_boards" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="powertrain_t26" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="data_t26" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="aquisition_boards" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="autonomous_t26" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,3826 +440,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K123"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="157" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Message: ACU</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x51</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ACU</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>ASSI_STATE</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>1=OFF, 2=READY, 3=DRIVING, 4=EMERGENCY, 5=FINISH</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>ACU_STATE</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>0=INIT, 1=MISSION_SELECT, 2=JETSON_WAITING, 3=INIT_SEQUENCE, 4=READY, 5=DRIVING, 6=EBS_ERROR, 7=EMERGENCY, 8=FINISHED, 9=MANUAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>ACU_CPU_TEMP</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Mission_select</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>AS_STATE</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>1=OFF, 2=READY, 3=DRIVING, 4=EMERGENCY, 5=FINISH</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>EMERGENCY</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>0=OFF, 1=ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>ASMS</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>0=OFF, 1=ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>IGN</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>0=OFF, 1=ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>EMERGENCY_cause</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>0=None, 1=SDC_OPEN, 2=RES, 3=Pressure_checks, 4=VCU_timeout, 5=Jetson_timeout, 6=ACU_WDT_TRIGGERED, 7=dir_actuator_timeout, 8=CAN_Dynamics_Pressure_timeout</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Message: CubeMars_Feedback</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x2968</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>-3200</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>3200</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Speed_RPM</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>1890</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>-320000</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>320000</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>ERPM</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>-60</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Driver_Temp</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>degC</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Error_Code</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>Message: CubeMars_possition_loop</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x468</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): JETSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>POSITION</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT1</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x710</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>BRK_PRESS</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>RES</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
-      <c r="J28" s="3" t="n"/>
-      <c r="K28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>BOTS</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n"/>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT2</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x720</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board2</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>WHEEL_ANGLE</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="n"/>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT3</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x730</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board3</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>WHEEL_ANGLE</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="3" t="n"/>
-      <c r="I37" s="3" t="n"/>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT4</t>
-        </is>
-      </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x740</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board4</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>ST_ANGLE</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>INERTIA</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="n"/>
-      <c r="J42" s="3" t="n"/>
-      <c r="K42" s="3" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>EMER_BUTTON</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3" t="n"/>
-      <c r="I43" s="3" t="n"/>
-      <c r="J43" s="3" t="n"/>
-      <c r="K43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT7</t>
-        </is>
-      </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x770</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Aquisition_Board7</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>BRK_PRESS</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3" t="n"/>
-      <c r="I47" s="3" t="n"/>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_IGN_R2D</t>
-        </is>
-      </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x600</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>ignition_manual</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="3" t="n"/>
-      <c r="I51" s="3" t="n"/>
-      <c r="J51" s="3" t="n"/>
-      <c r="K51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>r2d_manual</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3" t="n"/>
-      <c r="I52" s="3" t="n"/>
-      <c r="J52" s="3" t="n"/>
-      <c r="K52" s="3" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>ignition_auto</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="3" t="n"/>
-      <c r="I53" s="3" t="n"/>
-      <c r="J53" s="3" t="n"/>
-      <c r="K53" s="3" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>r2d_auto</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="3" t="n"/>
-      <c r="I54" s="3" t="n"/>
-      <c r="J54" s="3" t="n"/>
-      <c r="K54" s="3" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>shutdown_signal</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="3" t="n"/>
-      <c r="I55" s="3" t="n"/>
-      <c r="J55" s="3" t="n"/>
-      <c r="K55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>vcu_state</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="C56" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="3" t="n"/>
-      <c r="I56" s="3" t="n"/>
-      <c r="J56" s="3" t="n"/>
-      <c r="K56" s="3" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>R2D_button_raw</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C57" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3" t="n"/>
-      <c r="I57" s="3" t="n"/>
-      <c r="J57" s="3" t="n"/>
-      <c r="K57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Ignition_switch_raw</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C58" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3" t="n"/>
-      <c r="I58" s="3" t="n"/>
-      <c r="J58" s="3" t="n"/>
-      <c r="K58" s="3" t="inlineStr"/>
-    </row>
-    <row r="59"/>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>Message: DV_dynamics_1</t>
-        </is>
-      </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x500</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ACU</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>Speed_actual</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>km/h</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>Speed_target</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>km/h</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>Steering_angle_actual</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C64" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>-64</v>
-      </c>
-      <c r="I64" s="3" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>Steering_angle_target</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C65" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="3" t="n">
-        <v>-64</v>
-      </c>
-      <c r="I65" s="3" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½</t>
-        </is>
-      </c>
-      <c r="K65" s="3" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>Brake_hydr_actual</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C66" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>Brake_hydr_target</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="C67" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>Motor_moment_actual</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C68" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="3" t="n">
-        <v>-128</v>
-      </c>
-      <c r="I68" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="K68" s="3" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>Motor_moment_target</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C69" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="3" t="n">
-        <v>-128</v>
-      </c>
-      <c r="I69" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="inlineStr"/>
-    </row>
-    <row r="70"/>
-    <row r="71">
-      <c r="A71" s="1" t="inlineStr">
-        <is>
-          <t>Message: DV_dynamics_2</t>
-        </is>
-      </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x501</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ACU</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>Acceleration_longitudinal</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C73" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>0.001953125</v>
-      </c>
-      <c r="G73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="3" t="n"/>
-      <c r="I73" s="3" t="n"/>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>m/s2</t>
-        </is>
-      </c>
-      <c r="K73" s="3" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>Acceleration_lateral</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C74" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>0.001953125</v>
-      </c>
-      <c r="G74" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="3" t="n"/>
-      <c r="I74" s="3" t="n"/>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>m/s2</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>Yaw_rate</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C75" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>0.0078125</v>
-      </c>
-      <c r="G75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="3" t="n"/>
-      <c r="I75" s="3" t="n"/>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>ï¿½/s</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="inlineStr"/>
-    </row>
-    <row r="76"/>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_HV</t>
-        </is>
-      </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x81</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>HV</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F79" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="3" t="n"/>
-      <c r="I79" s="3" t="n"/>
-      <c r="J79" s="3" t="n"/>
-      <c r="K79" s="3" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>Brake_pressure_Front</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C80" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F80" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="3" t="n"/>
-      <c r="I80" s="3" t="n"/>
-      <c r="J80" s="3" t="n"/>
-      <c r="K80" s="3" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>Brake_pressure_Rear</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C81" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F81" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="3" t="n"/>
-      <c r="I81" s="3" t="n"/>
-      <c r="J81" s="3" t="n"/>
-      <c r="K81" s="3" t="inlineStr"/>
-    </row>
-    <row r="82"/>
-    <row r="83">
-      <c r="A83" s="1" t="inlineStr">
-        <is>
-          <t>Message: DV_status</t>
-        </is>
-      </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x502</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ACU</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>AS_status</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J85" s="3" t="n"/>
-      <c r="K85" s="3" t="inlineStr">
-        <is>
-          <t>1=AS_status_off, 2=AS_status_ready, 3=AS_status_driving, 4=AS_status_emergency, 5=AS_status_finished</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>ASB_EBS_state</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C86" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J86" s="3" t="n"/>
-      <c r="K86" s="3" t="inlineStr">
-        <is>
-          <t>1=ASB_EBS_state_deactivated, 2=ASB_EBS_state_initial_checkup_passed, 3=ASB_EBS_state_activated</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>AMI_state</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C87" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J87" s="3" t="n"/>
-      <c r="K87" s="3" t="inlineStr">
-        <is>
-          <t>1=AMI_state_acceleration, 2=AMI_state_skidpad, 3=AMI_state_trackdrive, 4=AMI_state_braketest, 5=AMI_state_inspection, 6=AMI_state_autocross</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>Steering_state</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C88" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="3" t="n"/>
-      <c r="K88" s="3" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>ASB_redundancy_state</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C89" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="n"/>
-      <c r="K89" s="3" t="inlineStr">
-        <is>
-          <t>1=ASB_redundancy_state_deactivated, 2=ASB_redundancy_state_engaged, 3=ASB_redundancy_state_initial_checkup_passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>Lap_counter</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="C90" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J90" s="3" t="n"/>
-      <c r="K90" s="3" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>Cones_count_actual</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C91" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J91" s="3" t="n"/>
-      <c r="K91" s="3" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>Cones_count_all</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C92" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="3" t="n">
-        <v>131071</v>
-      </c>
-      <c r="J92" s="3" t="n"/>
-      <c r="K92" s="3" t="inlineStr"/>
-    </row>
-    <row r="93"/>
-    <row r="94">
-      <c r="A94" s="1" t="inlineStr">
-        <is>
-          <t>Message: ASF_SIGNALS</t>
-        </is>
-      </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x511</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ACU</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>EBS_Pressure_Tank_Front</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C96" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3" t="n"/>
-      <c r="I96" s="3" t="n"/>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K96" s="3" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>EBS_Pressure_Tank_Rear</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C97" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F97" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="3" t="n"/>
-      <c r="I97" s="3" t="n"/>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K97" s="3" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>Brake_Pressure_Front</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C98" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F98" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="3" t="n"/>
-      <c r="I98" s="3" t="n"/>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K98" s="3" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>Brake_Pressure_Rear</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C99" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F99" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" s="3" t="n"/>
-      <c r="I99" s="3" t="n"/>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K99" s="3" t="inlineStr"/>
-    </row>
-    <row r="100"/>
-    <row r="101">
-      <c r="A101" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_RPM</t>
-        </is>
-      </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x509</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>rpm_actual</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C103" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F103" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" s="3" t="n">
-        <v>6000</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
-      <c r="K103" s="3" t="inlineStr"/>
-    </row>
-    <row r="104"/>
-    <row r="105">
-      <c r="A105" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_TORQUE_TARGET</t>
-        </is>
-      </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x49a</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): JETSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>torque_target</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C107" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F107" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" s="3" t="n">
-        <v>-100</v>
-      </c>
-      <c r="I107" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
-      <c r="K107" s="3" t="inlineStr"/>
-    </row>
-    <row r="108"/>
-    <row r="109">
-      <c r="A109" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_RPM_TARGET</t>
-        </is>
-      </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x499</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): JETSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K110" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>rpm_target</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C111" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F111" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G111" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H111" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" s="3" t="n">
-        <v>6000</v>
-      </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
-      <c r="K111" s="3" t="inlineStr"/>
-    </row>
-    <row r="112"/>
-    <row r="113">
-      <c r="A113" s="1" t="inlineStr">
-        <is>
-          <t>Message: JETSON</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x61</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>AS_STATE</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C115" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F115" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G115" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I115" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J115" s="3" t="n"/>
-      <c r="K115" s="3" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="3" t="inlineStr">
-        <is>
-          <t>AS_MISSION</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C116" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F116" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G116" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J116" s="3" t="n"/>
-      <c r="K116" s="3" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="3" t="inlineStr">
-        <is>
-          <t>TEMPERATURE</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C117" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F117" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G117" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H117" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I117" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J117" s="3" t="n"/>
-      <c r="K117" s="3" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C118" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F118" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G118" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J118" s="3" t="n"/>
-      <c r="K118" s="3" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>GPU</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C119" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F119" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G119" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J119" s="3" t="n"/>
-      <c r="K119" s="3" t="inlineStr"/>
-    </row>
-    <row r="120"/>
-    <row r="121">
-      <c r="A121" s="1" t="inlineStr">
-        <is>
-          <t>Message: RES</t>
-        </is>
-      </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x191</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K122" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="3" t="inlineStr">
-        <is>
-          <t>SIGNAL</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C123" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F123" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G123" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" s="3" t="n"/>
-      <c r="I123" s="3" t="n"/>
-      <c r="J123" s="3" t="n"/>
-      <c r="K123" s="3" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:K1068"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -37427,7 +33607,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38498,7 +34678,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -39874,4 +36054,3992 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K129"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="157" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Message: ACU</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x51</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ACU</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>ASSI_STATE</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>1=OFF, 2=READY, 3=DRIVING, 4=EMERGENCY, 5=FINISH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ACU_STATE</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>0=INIT, 1=MISSION_SELECT, 2=JETSON_WAITING, 3=INIT_SEQUENCE, 4=READY, 5=DRIVING, 6=EBS_ERROR, 7=EMERGENCY, 8=FINISHED, 9=MANUAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ACU_CPU_TEMP</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Mission_select</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>AS_STATE</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>1=OFF, 2=READY, 3=DRIVING, 4=EMERGENCY, 5=FINISH</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>EMERGENCY</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>0=OFF, 1=ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>ASMS</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>0=OFF, 1=ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>IGN</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>0=OFF, 1=ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>EMERGENCY_cause</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>0=None, 1=SDC_OPEN, 2=RES, 3=Pressure_checks, 4=VCU_timeout, 5=Jetson_timeout, 6=ACU_WDT_TRIGGERED, 7=dir_actuator_timeout, 8=CAN_Dynamics_Pressure_timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Message: CubeMars_Feedback</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x2968</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>-3200</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Speed_RPM</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1890</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>-320000</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>320000</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>ERPM</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Driver_Temp</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Error_Code</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Message: CubeMars_possition_loop</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x468</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>POSITION</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT1</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x710</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>BRK_PRESS</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>BOTS</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT2</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x720</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>WHEEL_ANGLE</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT3</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x730</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>WHEEL_ANGLE</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT4</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x740</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>ST_ANGLE</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>INERTIA</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3" t="n"/>
+      <c r="I42" s="3" t="n"/>
+      <c r="J42" s="3" t="n"/>
+      <c r="K42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>EMER_BUTTON</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" s="3" t="n"/>
+      <c r="K43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT7</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x770</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Aquisition_Board7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>BRK_PRESS</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_IGN_R2D</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x600</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>ignition_manual</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" s="3" t="n"/>
+      <c r="J51" s="3" t="n"/>
+      <c r="K51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>r2d_manual</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="n"/>
+      <c r="I52" s="3" t="n"/>
+      <c r="J52" s="3" t="n"/>
+      <c r="K52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>ignition_auto</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3" t="n"/>
+      <c r="I53" s="3" t="n"/>
+      <c r="J53" s="3" t="n"/>
+      <c r="K53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>r2d_auto</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3" t="n"/>
+      <c r="I54" s="3" t="n"/>
+      <c r="J54" s="3" t="n"/>
+      <c r="K54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>shutdown_signal</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3" t="n"/>
+      <c r="I55" s="3" t="n"/>
+      <c r="J55" s="3" t="n"/>
+      <c r="K55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>vcu_state</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3" t="n"/>
+      <c r="I56" s="3" t="n"/>
+      <c r="J56" s="3" t="n"/>
+      <c r="K56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>R2D_button_raw</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3" t="n"/>
+      <c r="I57" s="3" t="n"/>
+      <c r="J57" s="3" t="n"/>
+      <c r="K57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Ignition_switch_raw</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3" t="n"/>
+      <c r="I58" s="3" t="n"/>
+      <c r="J58" s="3" t="n"/>
+      <c r="K58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>Message: DV_dynamics_1</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x500</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Speed_actual</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Speed_target</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Steering_angle_actual</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>-64</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Steering_angle_target</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>-64</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Brake_hydr_actual</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Brake_hydr_target</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Motor_moment_actual</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>-128</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Motor_moment_target</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>-128</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70"/>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>Message: DV_dynamics_2</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x501</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Acceleration_longitudinal</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0.001953125</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="3" t="n"/>
+      <c r="I73" s="3" t="n"/>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>m/s2</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Acceleration_lateral</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>0.001953125</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="3" t="n"/>
+      <c r="I74" s="3" t="n"/>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>m/s2</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Yaw_rate</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0.0078125</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="3" t="n"/>
+      <c r="I75" s="3" t="n"/>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>ï¿½/s</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76"/>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_HV</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x81</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="3" t="n"/>
+      <c r="I79" s="3" t="n"/>
+      <c r="J79" s="3" t="n"/>
+      <c r="K79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Brake_pressure_Front</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="3" t="n"/>
+      <c r="I80" s="3" t="n"/>
+      <c r="J80" s="3" t="n"/>
+      <c r="K80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Brake_pressure_Rear</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3" t="n"/>
+      <c r="I81" s="3" t="n"/>
+      <c r="J81" s="3" t="n"/>
+      <c r="K81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82"/>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>Message: DV_status</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x502</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ACU</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>AS_status</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J85" s="3" t="n"/>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>1=AS_status_off, 2=AS_status_ready, 3=AS_status_driving, 4=AS_status_emergency, 5=AS_status_finished</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>ASB_EBS_state</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J86" s="3" t="n"/>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>1=ASB_EBS_state_deactivated, 2=ASB_EBS_state_initial_checkup_passed, 3=ASB_EBS_state_activated</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>AMI_state</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J87" s="3" t="n"/>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>1=AMI_state_acceleration, 2=AMI_state_skidpad, 3=AMI_state_trackdrive, 4=AMI_state_braketest, 5=AMI_state_inspection, 6=AMI_state_autocross</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>Steering_state</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" s="3" t="n"/>
+      <c r="K88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>ASB_redundancy_state</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3" t="n"/>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>1=ASB_redundancy_state_deactivated, 2=ASB_redundancy_state_engaged, 3=ASB_redundancy_state_initial_checkup_passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>Lap_counter</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J90" s="3" t="n"/>
+      <c r="K90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Cones_count_actual</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J91" s="3" t="n"/>
+      <c r="K91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Cones_count_all</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>131071</v>
+      </c>
+      <c r="J92" s="3" t="n"/>
+      <c r="K92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93"/>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>Message: ASF_SIGNALS</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x511</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ACU</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>EBS_Pressure_Tank_Front</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3" t="n"/>
+      <c r="I96" s="3" t="n"/>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>EBS_Pressure_Tank_Rear</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="3" t="n"/>
+      <c r="I97" s="3" t="n"/>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>Brake_Pressure_Front</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="3" t="n"/>
+      <c r="I98" s="3" t="n"/>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Brake_Pressure_Rear</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="3" t="n"/>
+      <c r="I99" s="3" t="n"/>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_RPM</t>
+        </is>
+      </c>
+      <c r="B101" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x509</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>rpm_actual</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104"/>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_TORQUE_TARGET</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x49a</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>torque_target</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="3" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I107" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108"/>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_RPM_TARGET</t>
+        </is>
+      </c>
+      <c r="B109" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x499</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>rpm_target</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112"/>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>Message: JETSON</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x61</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>AS_STATE</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J115" s="3" t="n"/>
+      <c r="K115" s="3" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>AS_MISSION</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J116" s="3" t="n"/>
+      <c r="K116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>TEMPERATURE</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J117" s="3" t="n"/>
+      <c r="K117" s="3" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J118" s="3" t="n"/>
+      <c r="K118" s="3" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J119" s="3" t="n"/>
+      <c r="K119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120"/>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>Message: RES</t>
+        </is>
+      </c>
+      <c r="B121" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x191</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): RES</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>SIGNAL</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="3" t="n"/>
+      <c r="I123" s="3" t="n"/>
+      <c r="J123" s="3" t="n"/>
+      <c r="K123" s="3" t="inlineStr"/>
+    </row>
+    <row r="124"/>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>Message: SLAM_STATS</t>
+        </is>
+      </c>
+      <c r="B125" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x505</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>Lap_counter</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" s="3" t="n"/>
+      <c r="I127" s="3" t="n"/>
+      <c r="J127" s="3" t="n"/>
+      <c r="K127" s="3" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>Cones_count_actual</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" s="3" t="n"/>
+      <c r="I128" s="3" t="n"/>
+      <c r="J128" s="3" t="n"/>
+      <c r="K128" s="3" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>Cones_count_all</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" s="3" t="n"/>
+      <c r="I129" s="3" t="n"/>
+      <c r="J129" s="3" t="n"/>
+      <c r="K129" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -39875,7 +39875,7 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>Message: SLAM_STATS</t>
+          <t>Message: SLAM_STATS_CAN</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -19186,7 +19186,7 @@
         <v>48</v>
       </c>
       <c r="C607" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D607" s="3" t="inlineStr">
         <is>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -36065,7 +36065,7 @@
   <dimension ref="A1:K129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -36749,7 +36749,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Message: CubeMars_possition_loop</t>
+          <t>Message: CubeMars_position_loop</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1068"/>
+  <dimension ref="A1:K1072"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -33589,7 +33589,7 @@
         </is>
       </c>
       <c r="E1068" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1068" s="3" t="n">
         <v>0.01</v>
@@ -33601,6 +33601,116 @@
       <c r="I1068" s="3" t="n"/>
       <c r="J1068" s="3" t="n"/>
       <c r="K1068" s="3" t="inlineStr"/>
+    </row>
+    <row r="1069"/>
+    <row r="1070">
+      <c r="A1070" s="1" t="inlineStr">
+        <is>
+          <t>Message: Master_MSC_ID_4</t>
+        </is>
+      </c>
+      <c r="B1070" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x706</t>
+        </is>
+      </c>
+      <c r="C1070" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): AMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B1071" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C1071" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D1071" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E1071" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F1071" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G1071" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H1071" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I1071" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J1071" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K1071" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="3" t="inlineStr">
+        <is>
+          <t>slaves_detected</t>
+        </is>
+      </c>
+      <c r="B1072" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1072" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1072" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E1072" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F1072" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1072" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1072" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1072" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="J1072" s="3" t="n"/>
+      <c r="K1072" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -19488,7 +19488,7 @@
       <c r="J616" s="3" t="n"/>
       <c r="K616" s="3" t="inlineStr">
         <is>
-          <t>0=START, 1=OPEN_ALL, 2=SWITCH_HVNEG, 3=DELAY1, 4=VERIFY1, 5=SWITCH_PRECHARGE, 6=DELAY2, 7=VERIFY2, 8=VERIFY_CURRENT, 9=VERIFY_BUS_VOLT, 10=SWITCH_HVPOS, 11=DELAY3, 12=VERIFY3, 13=TURN_OFF_PRECHARGE, 14=DELAY4, 15=VERIFY4, 16=END, 17=WRONG, 18=KILL, 19=RX_CAN</t>
+          <t>0=START, 1=OPEN_ALL, 2=SWITCH_HVNEG, 3=WAIT_FOR_AIR_NEG_TO_CLOSE, 4=CHECKING_AIR_NEG_IS_CLOSED, 5=SWITCH_PRECHARGE, 6=WAIT_FOR_PRECHARGE_TO_CLOSE, 7=CHECKING_PRECHARGE_IS_CLOSED, 8=VERIFY_CURRENT, 9=VERIFY_BUS_VOLT, 10=SWITCH_HVPOS, 11=WAIT_FOR_AIR_POS_TO_CLOSE, 12=CHECKING_AIR_POS_IS_CLOSED, 13=TURN_OFF_PRECHARGE, 14=WAIT_FOR_PRECHARGE_TO_OPEN, 15=CHECKING_PRECHARGE_IS_OPEN, 16=END, 17=WRONG, 18=KILL, 19=RX_CAN</t>
         </is>
       </c>
     </row>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -36172,7 +36172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -36603,7 +36603,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>Sender(s): Unknown</t>
+          <t>Sender(s): AK10_9</t>
         </is>
       </c>
     </row>
@@ -39875,229 +39875,233 @@
       <c r="J119" s="3" t="n"/>
       <c r="K119" s="3" t="inlineStr"/>
     </row>
-    <row r="120"/>
-    <row r="121">
-      <c r="A121" s="1" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>EMERGENCY_CAUSE</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="3" t="n"/>
+      <c r="I120" s="3" t="n"/>
+      <c r="J120" s="3" t="n"/>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>0=None, 1=ACU, 2=ZED, 3=Steering, 4=Planner, 5=SLAM, 6=P-Puma, 7=IMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="121"/>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
         <is>
           <t>Message: RES</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
+      <c r="B122" s="1" t="inlineStr">
         <is>
           <t>ID: 0x191</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>Sender(s): RES</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>Signal Name</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>Start Bit</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
         <is>
           <t>Length (bits)</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Byte Order</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Signed</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>Offset</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr">
+      <c r="I123" s="2" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="J122" s="2" t="inlineStr">
+      <c r="J123" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="K122" s="2" t="inlineStr">
+      <c r="K123" s="2" t="inlineStr">
         <is>
           <t>Choices</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="3" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
         <is>
           <t>SIGNAL</t>
         </is>
       </c>
-      <c r="B123" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C123" s="3" t="n">
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F123" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G123" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" s="3" t="n"/>
-      <c r="I123" s="3" t="n"/>
-      <c r="J123" s="3" t="n"/>
-      <c r="K123" s="3" t="inlineStr"/>
-    </row>
-    <row r="124"/>
-    <row r="125">
-      <c r="A125" s="1" t="inlineStr">
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="3" t="n"/>
+      <c r="I124" s="3" t="n"/>
+      <c r="J124" s="3" t="n"/>
+      <c r="K124" s="3" t="inlineStr"/>
+    </row>
+    <row r="125"/>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
         <is>
           <t>Message: SLAM_STATS_CAN</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
+      <c r="B126" s="1" t="inlineStr">
         <is>
           <t>ID: 0x505</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>Sender(s): JETSON</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>Signal Name</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>Start Bit</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
         <is>
           <t>Length (bits)</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Byte Order</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Signed</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>Offset</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr">
+      <c r="I127" s="2" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="J126" s="2" t="inlineStr">
+      <c r="J127" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="K126" s="2" t="inlineStr">
+      <c r="K127" s="2" t="inlineStr">
         <is>
           <t>Choices</t>
         </is>
       </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>Lap_counter</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C127" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F127" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G127" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H127" s="3" t="n"/>
-      <c r="I127" s="3" t="n"/>
-      <c r="J127" s="3" t="n"/>
-      <c r="K127" s="3" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>Cones_count_actual</t>
+          <t>Lap_counter</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
         <v>4</v>
-      </c>
-      <c r="C128" s="3" t="n">
-        <v>8</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
@@ -40121,14 +40125,14 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>Cones_count_all</t>
+          <t>Cones_count_actual</t>
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C129" s="3" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
@@ -40149,6 +40153,37 @@
       <c r="J129" s="3" t="n"/>
       <c r="K129" s="3" t="inlineStr"/>
     </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>Cones_count_all</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" s="3" t="n"/>
+      <c r="I130" s="3" t="n"/>
+      <c r="J130" s="3" t="n"/>
+      <c r="K130" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -23966,7 +23966,7 @@
       </c>
       <c r="J759" s="3" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>ï¿½C</t>
         </is>
       </c>
       <c r="K759" s="3" t="inlineStr"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="powertrain_t26" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="data_t26" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="aquisition_boards" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="autonomous_t26" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="eveurope_charger" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="data_t26" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="aquisition_boards" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="autonomous_t26" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33723,6 +33724,1757 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="64" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Message: BMS_ChargingRequest</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x1806e8f4</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): BMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Max_Charging_Voltage</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>6553.5</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Max_Charging_Current</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>6553.5</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Message: Charger_Status</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x18ff50e8</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Charger</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Output_Voltage</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>6553.5</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Output_Current</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>6553.5</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>HW_Failure</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>0=Normal, 1=Hardware_Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Temp_OTP</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>0=Normal, 1=Over_Temperature_Protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Input_Voltage_Fault</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>0=Normal_Input_Voltage, 1=Incorrect_Input_Voltage_Charger_Stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Starting_State_Fault</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>0=Normal_Battery_Connected, 1=Battery_Disconnecting_or_Reverse</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Comm_Timeout</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>0=Normal_Communication, 1=Receiving_Timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Charger_Temperature</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>-40</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Message: BMS_ChargingRequest_P998</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x1806e7f4</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): BMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Max_Charging_Voltage</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>6553.5</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Max_Charging_Current</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>6553.5</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J22" s="3" t="n"/>
+      <c r="K22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Message: Charger_Status_P998</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x18ff50e7</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Charger</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Output_Voltage</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>6553.5</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Output_Current</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>6553.5</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>HW_Failure</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>0=Normal, 1=Hardware_Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Temp_OTP</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>0=Normal, 1=Over_Temperature_Protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Input_Voltage_Fault</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="3" t="n"/>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>0=Normal_Input_Voltage, 1=Incorrect_Input_Voltage_Charger_Stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Starting_State_Fault</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="3" t="n"/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>0=Normal_Battery_Connected, 1=Battery_Disconnecting_or_Reverse</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Comm_Timeout</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>0=Normal_Communication, 1=Receiving_Timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Charger_Temperature</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>-40</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Message: BMS_ChargingRequest_P1000</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x1806e5f4</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): BMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Max_Charging_Voltage</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>6553.5</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Max_Charging_Current</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>6553.5</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Message: Charger_Status_P1000</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x18ff50e5</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Charger</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Output_Voltage</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>6553.5</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Output_Current</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>6553.5</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>HW_Failure</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="3" t="n"/>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>0=Normal, 1=Hardware_Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Temp_OTP</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="3" t="n"/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>0=Normal, 1=Over_Temperature_Protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Input_Voltage_Fault</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="3" t="n"/>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>0=Normal_Input_Voltage, 1=Incorrect_Input_Voltage_Charger_Stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Starting_State_Fault</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="3" t="n"/>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>0=Normal_Battery_Connected, 1=Battery_Disconnecting_or_Reverse</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Comm_Timeout</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="3" t="n"/>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>0=Normal_Communication, 1=Receiving_Timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Charger_Temperature</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>-40</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -34788,7 +36540,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36166,7 +37918,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -8,10 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="powertrain_t26" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="eveurope_charger" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="data_t26" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="aquisition_boards" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="autonomous_t26" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="data_t26" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="aquisition_boards" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="autonomous_t26" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1072"/>
+  <dimension ref="A1:K1076"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -564,7 +563,11 @@
           <t>ON/OFF</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>0=PRECHARGE OFF, 1=BALANCING ON</t>
+        </is>
+      </c>
     </row>
     <row r="4"/>
     <row r="5">
@@ -33064,7 +33067,11 @@
           <t>ON/OFF</t>
         </is>
       </c>
-      <c r="K1049" s="3" t="inlineStr"/>
+      <c r="K1049" s="3" t="inlineStr">
+        <is>
+          <t>0=BALANCING OFF, 1=BALANCING ON</t>
+        </is>
+      </c>
     </row>
     <row r="1050"/>
     <row r="1051">
@@ -33712,6 +33719,120 @@
       </c>
       <c r="J1072" s="3" t="n"/>
       <c r="K1072" s="3" t="inlineStr"/>
+    </row>
+    <row r="1073"/>
+    <row r="1074">
+      <c r="A1074" s="1" t="inlineStr">
+        <is>
+          <t>Message: Start_Charging</t>
+        </is>
+      </c>
+      <c r="B1074" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x81</t>
+        </is>
+      </c>
+      <c r="C1074" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B1075" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C1075" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D1075" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E1075" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F1075" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G1075" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H1075" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I1075" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J1075" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K1075" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="3" t="inlineStr">
+        <is>
+          <t>Charging_Request</t>
+        </is>
+      </c>
+      <c r="B1076" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1076" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1076" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E1076" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F1076" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1076" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1076" s="3" t="n"/>
+      <c r="I1076" s="3" t="n"/>
+      <c r="J1076" s="3" t="inlineStr">
+        <is>
+          <t>ON/OFF</t>
+        </is>
+      </c>
+      <c r="K1076" s="3" t="inlineStr">
+        <is>
+          <t>0=CHARGING OFF, 1=CHARGING ON</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -33719,1757 +33840,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K50"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="64" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Message: BMS_ChargingRequest</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x1806e8f4</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): BMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Max_Charging_Voltage</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>6553.5</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Max_Charging_Current</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>6553.5</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Message: Charger_Status</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x18ff50e8</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Charger</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Output_Voltage</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>6553.5</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Output_Current</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>6553.5</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>HW_Failure</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>0=Normal, 1=Hardware_Failure</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Temp_OTP</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>0=Normal, 1=Over_Temperature_Protection</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Input_Voltage_Fault</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>0=Normal_Input_Voltage, 1=Incorrect_Input_Voltage_Charger_Stop</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Starting_State_Fault</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>0=Normal_Battery_Connected, 1=Battery_Disconnecting_or_Reverse</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Comm_Timeout</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>0=Normal_Communication, 1=Receiving_Timeout</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Charger_Temperature</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>-40</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>-40</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>215</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>degC</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Message: BMS_ChargingRequest_P998</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x1806e7f4</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): BMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Max_Charging_Voltage</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>6553.5</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Max_Charging_Current</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>6553.5</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J22" s="3" t="n"/>
-      <c r="K22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>Message: Charger_Status_P998</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x18ff50e7</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Charger</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Output_Voltage</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>6553.5</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Output_Current</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>6553.5</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>HW_Failure</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="3" t="n"/>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>0=Normal, 1=Hardware_Failure</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Temp_OTP</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>0=Normal, 1=Over_Temperature_Protection</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Input_Voltage_Fault</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>0=Normal_Input_Voltage, 1=Incorrect_Input_Voltage_Charger_Stop</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Starting_State_Fault</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>0=Normal_Battery_Connected, 1=Battery_Disconnecting_or_Reverse</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Comm_Timeout</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="3" t="n"/>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>0=Normal_Communication, 1=Receiving_Timeout</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Charger_Temperature</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>-40</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>-40</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>215</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>degC</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>Message: BMS_ChargingRequest_P1000</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x1806e5f4</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): BMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Max_Charging_Voltage</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>6553.5</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Max_Charging_Current</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>6553.5</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J39" s="3" t="n"/>
-      <c r="K39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>Message: Charger_Status_P1000</t>
-        </is>
-      </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x18ff50e5</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Charger</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Output_Voltage</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>6553.5</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Output_Current</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>6553.5</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>HW_Failure</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C45" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="3" t="n"/>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>0=Normal, 1=Hardware_Failure</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Temp_OTP</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="3" t="n"/>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>0=Normal, 1=Over_Temperature_Protection</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Input_Voltage_Fault</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="3" t="n"/>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>0=Normal_Input_Voltage, 1=Incorrect_Input_Voltage_Charger_Stop</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Starting_State_Fault</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="C48" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="3" t="n"/>
-      <c r="K48" s="3" t="inlineStr">
-        <is>
-          <t>0=Normal_Battery_Connected, 1=Battery_Disconnecting_or_Reverse</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Comm_Timeout</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="3" t="n"/>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>0=Normal_Communication, 1=Receiving_Timeout</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Charger_Temperature</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="C50" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>-40</v>
-      </c>
-      <c r="H50" s="3" t="n">
-        <v>-40</v>
-      </c>
-      <c r="I50" s="3" t="n">
-        <v>215</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>degC</t>
-        </is>
-      </c>
-      <c r="K50" s="3" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36540,7 +34910,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37918,7 +36288,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -4433,7 +4433,7 @@
         <v>0</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="G98" s="3" t="n">
         <v>0</v>
@@ -4468,7 +4468,7 @@
         <v>0</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>0</v>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -1371,7 +1371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K132"/>
+  <dimension ref="A1:K135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -4630,7 +4630,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>rpm_actual</t>
+          <t>motor_rpm_left</t>
         </is>
       </c>
       <c r="B105" s="3" t="n">
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="E105" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F105" s="3" t="n">
         <v>1</v>
@@ -4666,425 +4666,425 @@
       </c>
       <c r="K105" s="3" t="inlineStr"/>
     </row>
-    <row r="106"/>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>motor_rpm_right</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="3" t="n"/>
+      <c r="I106" s="3" t="n"/>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr"/>
+    </row>
     <row r="107">
-      <c r="A107" s="1" t="inlineStr">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>motor_current_left</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="3" t="n"/>
+      <c r="I107" s="3" t="n"/>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>motor_current_right</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="3" t="n"/>
+      <c r="I108" s="3" t="n"/>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109"/>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
         <is>
           <t>Message: VCU_TORQUE_TARGET</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
+      <c r="B110" s="1" t="inlineStr">
         <is>
           <t>ID: 0x49a</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>Sender(s): JETSON</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>Signal Name</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Start Bit</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>Length (bits)</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Byte Order</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Signed</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>Offset</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="J108" s="2" t="inlineStr">
+      <c r="J111" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="K108" s="2" t="inlineStr">
+      <c r="K111" s="2" t="inlineStr">
         <is>
           <t>Choices</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="3" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
         <is>
           <t>torque_target</t>
         </is>
       </c>
-      <c r="B109" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C109" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F109" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G109" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" s="3" t="n">
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="3" t="n">
         <v>-100</v>
       </c>
-      <c r="I109" s="3" t="n">
+      <c r="I112" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="J109" s="3" t="inlineStr">
+      <c r="J112" s="3" t="inlineStr">
         <is>
           <t>RPM</t>
         </is>
       </c>
-      <c r="K109" s="3" t="inlineStr"/>
-    </row>
-    <row r="110"/>
-    <row r="111">
-      <c r="A111" s="1" t="inlineStr">
+      <c r="K112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113"/>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
         <is>
           <t>Message: VCU_RPM_TARGET</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
+      <c r="B114" s="1" t="inlineStr">
         <is>
           <t>ID: 0x499</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>Sender(s): JETSON</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>Signal Name</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>Start Bit</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
         <is>
           <t>Length (bits)</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Byte Order</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Signed</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>Offset</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="J112" s="2" t="inlineStr">
+      <c r="J115" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="K112" s="2" t="inlineStr">
+      <c r="K115" s="2" t="inlineStr">
         <is>
           <t>Choices</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="3" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t>rpm_target</t>
         </is>
       </c>
-      <c r="B113" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C113" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F113" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G113" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" s="3" t="n">
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="J113" s="3" t="inlineStr">
+      <c r="J116" s="3" t="inlineStr">
         <is>
           <t>RPM</t>
         </is>
       </c>
-      <c r="K113" s="3" t="inlineStr"/>
-    </row>
-    <row r="114"/>
-    <row r="115">
-      <c r="A115" s="1" t="inlineStr">
+      <c r="K116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117"/>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
         <is>
           <t>Message: JETSON</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
+      <c r="B118" s="1" t="inlineStr">
         <is>
           <t>ID: 0x61</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>Sender(s): JETSON</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>Signal Name</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>Start Bit</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
         <is>
           <t>Length (bits)</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Byte Order</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Signed</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>Offset</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr">
+      <c r="I119" s="2" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="J116" s="2" t="inlineStr">
+      <c r="J119" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="K116" s="2" t="inlineStr">
+      <c r="K119" s="2" t="inlineStr">
         <is>
           <t>Choices</t>
         </is>
       </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="3" t="inlineStr">
-        <is>
-          <t>AS_STATE</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C117" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F117" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G117" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H117" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I117" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J117" s="3" t="n"/>
-      <c r="K117" s="3" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>AS_MISSION</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C118" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F118" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G118" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J118" s="3" t="n"/>
-      <c r="K118" s="3" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>TEMPERATURE</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C119" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F119" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G119" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J119" s="3" t="n"/>
-      <c r="K119" s="3" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>AS_STATE</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>0</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="J120" s="3" t="n"/>
       <c r="K120" s="3" t="inlineStr"/>
@@ -5112,14 +5112,14 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>GPU</t>
+          <t>AS_MISSION</t>
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>0</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="J121" s="3" t="n"/>
       <c r="K121" s="3" t="inlineStr"/>
@@ -5147,11 +5147,11 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>EMERGENCY_CAUSE</t>
+          <t>TEMPERATURE</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>8</v>
@@ -5170,288 +5170,393 @@
       <c r="G122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H122" s="3" t="n"/>
-      <c r="I122" s="3" t="n"/>
+      <c r="H122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="J122" s="3" t="n"/>
-      <c r="K122" s="3" t="inlineStr">
+      <c r="K122" s="3" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J123" s="3" t="n"/>
+      <c r="K123" s="3" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J124" s="3" t="n"/>
+      <c r="K124" s="3" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>EMERGENCY_CAUSE</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="3" t="n"/>
+      <c r="I125" s="3" t="n"/>
+      <c r="J125" s="3" t="n"/>
+      <c r="K125" s="3" t="inlineStr">
         <is>
           <t>0=None, 1=ACU, 2=ZED, 3=Steering, 4=Planner, 5=SLAM, 6=P-Puma, 7=IMU</t>
         </is>
       </c>
     </row>
-    <row r="123"/>
-    <row r="124">
-      <c r="A124" s="1" t="inlineStr">
+    <row r="126"/>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
         <is>
           <t>Message: RES</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
+      <c r="B127" s="1" t="inlineStr">
         <is>
           <t>ID: 0x191</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>Sender(s): RES</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>Signal Name</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>Start Bit</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t>Length (bits)</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Byte Order</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Signed</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>Offset</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr">
+      <c r="I128" s="2" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="J125" s="2" t="inlineStr">
+      <c r="J128" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="K125" s="2" t="inlineStr">
+      <c r="K128" s="2" t="inlineStr">
         <is>
           <t>Choices</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="3" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
         <is>
           <t>SIGNAL</t>
         </is>
       </c>
-      <c r="B126" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C126" s="3" t="n">
+      <c r="B129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F126" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G126" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" s="3" t="n"/>
-      <c r="I126" s="3" t="n"/>
-      <c r="J126" s="3" t="n"/>
-      <c r="K126" s="3" t="inlineStr"/>
-    </row>
-    <row r="127"/>
-    <row r="128">
-      <c r="A128" s="1" t="inlineStr">
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" s="3" t="n"/>
+      <c r="I129" s="3" t="n"/>
+      <c r="J129" s="3" t="n"/>
+      <c r="K129" s="3" t="inlineStr"/>
+    </row>
+    <row r="130"/>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
         <is>
           <t>Message: SLAM_STATS_CAN</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
+      <c r="B131" s="1" t="inlineStr">
         <is>
           <t>ID: 0x505</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>Sender(s): JETSON</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>Signal Name</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>Start Bit</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
         <is>
           <t>Length (bits)</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Byte Order</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Signed</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>Offset</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="J129" s="2" t="inlineStr">
+      <c r="J132" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="K129" s="2" t="inlineStr">
+      <c r="K132" s="2" t="inlineStr">
         <is>
           <t>Choices</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="3" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
         <is>
           <t>Lap_counter</t>
         </is>
       </c>
-      <c r="B130" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C130" s="3" t="n">
+      <c r="B133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C133" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F130" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G130" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" s="3" t="n"/>
-      <c r="I130" s="3" t="n"/>
-      <c r="J130" s="3" t="n"/>
-      <c r="K130" s="3" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="3" t="inlineStr">
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" s="3" t="n"/>
+      <c r="I133" s="3" t="n"/>
+      <c r="J133" s="3" t="n"/>
+      <c r="K133" s="3" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
         <is>
           <t>Cones_count_actual</t>
         </is>
       </c>
-      <c r="B131" s="3" t="n">
+      <c r="B134" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C131" s="3" t="n">
+      <c r="C134" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F131" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G131" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" s="3" t="n"/>
-      <c r="I131" s="3" t="n"/>
-      <c r="J131" s="3" t="n"/>
-      <c r="K131" s="3" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="3" t="inlineStr">
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" s="3" t="n"/>
+      <c r="I134" s="3" t="n"/>
+      <c r="J134" s="3" t="n"/>
+      <c r="K134" s="3" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
         <is>
           <t>Cones_count_all</t>
         </is>
       </c>
-      <c r="B132" s="3" t="n">
+      <c r="B135" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C132" s="3" t="n">
+      <c r="C135" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F132" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G132" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" s="3" t="n"/>
-      <c r="I132" s="3" t="n"/>
-      <c r="J132" s="3" t="n"/>
-      <c r="K132" s="3" t="inlineStr"/>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" s="3" t="n"/>
+      <c r="I135" s="3" t="n"/>
+      <c r="J135" s="3" t="n"/>
+      <c r="K135" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -11,6 +11,7 @@
     <sheet name="autonomous_t26" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="powertrain_t26" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="aquisition_boards" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="FSIC" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40344,4 +40345,7542 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K239"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="223" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV1_ERPM_DUTY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x404</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_INV1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Actual_ERPM</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>-120000</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>120000</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>ERPM</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Actual_Duty</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Actual_InputVoltage</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV1_AC_DC_current</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x424</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_INV1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Actual_ACCurrent</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Apk</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Actual_DCCurrent</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV1_Temperatures</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x444</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_INV1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Actual_TempController</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>-55</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Actual_TempMotor</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>-55</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Actual_FaultCode</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>0=NO_FAULT, 1=OVERVOLTAGE, 2=UNDERVOLTAGE, 3=DRV_ERROR, 4=ABS_MAX_OVERCURRENT, 5=CONTROLLER_OVERTEMPERATURE, 6=MOTOR_OVERTEMPERATURE, 7=SENSOR_WIRE_FAULT, 8=SENSOR_GENERAL_FAULT, 9=CAN_COMMAND_ERROR, 10=ANALOG_INPUT_ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV1_FOC</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x464</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_INV1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Actual_FOC_id</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Apk</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Actual_FOC_iq</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Apk</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV1_MISC</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x484</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_INV1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Actual_Throttle</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Actual_Brake</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Digital_output_4</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Digital_output_3</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Digital_output_2</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Digital_output_1</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="3" t="n"/>
+      <c r="K30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Digital_input_4</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="3" t="n"/>
+      <c r="K31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Digital_input_3</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Digital_input_2</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Digital_input_1</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="3" t="n"/>
+      <c r="K34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Drive_enable</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Motor_temp_limit</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="3" t="n"/>
+      <c r="K36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Motor_accel_limit</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="3" t="n"/>
+      <c r="K37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Input_voltage_limit</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="3" t="n"/>
+      <c r="K38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>INV1_IGBT_temp_limit</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>INV1_IGBT_accel_limit</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="3" t="n"/>
+      <c r="K40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Drive_enable_limit</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="3" t="n"/>
+      <c r="K41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>INV1_DC_current_limit</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="3" t="n"/>
+      <c r="K42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Capacitor_temp_limit</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="3" t="n"/>
+      <c r="K43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>INV1_Power_limit</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="3" t="n"/>
+      <c r="K44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>INV1_RPM_max_limit</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="3" t="n"/>
+      <c r="K45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>INV1_RPM_min_limit</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="3" t="n"/>
+      <c r="K46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>INV1_CAN_map_version</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV1_TargetIq</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x3e4</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_INV1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>INV1_ControlMode</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>INV1_TargetIq</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>Apk</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>INV1_MotorPosition</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>359</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>INV1_isMotorStill</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV1_MinMaxAcCurrent</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x4a4</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_INV1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>INV1_MaxAcCurrent</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>Apk</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>INV1_AvailableMaxAcCurrent</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>Apk</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>INV1_MinAcCurrent</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>Apk</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>INV1_AvailableMinAcCurrent</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>Apk</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62"/>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV1_MinMaxDcCurrent</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x4c4</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_INV1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>INV1_MaxDcCurrent</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>Adc</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>INV1_AvailableMaxDcCurrent</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>Adc</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>INV1_MinDcCurrent</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>Adc</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>INV1_AvailableMinDcCurrent</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>Adc</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69"/>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV1_SetDriveEnable</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x184</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>INV1_CMD_DriveEnable</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" s="3" t="n"/>
+      <c r="K72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73"/>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV1_SetAcCurrent</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x24</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>INV1_CMD_TargetAcCurrent</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77"/>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV1_SetBrakeCurrent</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x44</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>INV1_CMD_TargetBrakeCurrent</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81"/>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV1_SetERPM</t>
+        </is>
+      </c>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x64</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>INV1_CMD_TargetSpeed</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>ERPM</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr"/>
+    </row>
+    <row r="85"/>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV1_SetPosition</t>
+        </is>
+      </c>
+      <c r="B86" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x84</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>INV1_CMD_TargetPosition</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>359</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89"/>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV1_SetRelCurrent</t>
+        </is>
+      </c>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0xa4</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>INV1_CMD_TargetRelativeCurrent</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93"/>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV1_SetRelBrakeCurrent</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0xc4</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>INV1_CMD_TgtRelBrakeCurrent</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97"/>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV1_SetDigOutput</t>
+        </is>
+      </c>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0xe4</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>INV1_CMD_SetDigOutput4</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>INV1_CMD_SetDigOutput3</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>INV1_CMD_SetDigOutput2</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>INV1_CMD_SetDigOutput1</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104"/>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV1_SetMaxAcCurrent</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x104</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>INV1_CMD_MaxAcCurrent</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108"/>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV1_SetMaxAcBrakeCurrent</t>
+        </is>
+      </c>
+      <c r="B109" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x124</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>INV1_CMD_MaxAcBrakeCurrent</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112"/>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV1_SetMaxDcCurrent</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x144</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>INV1_CMD_MaxDcCurrent</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr"/>
+    </row>
+    <row r="116"/>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV1_SetMaxDcBrakeCurrent</t>
+        </is>
+      </c>
+      <c r="B117" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x164</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>INV1_CMD_MaxDcBrakeCurrent</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120"/>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV2_ERPM_DUTY_VOLTAGE</t>
+        </is>
+      </c>
+      <c r="B121" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x405</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_INV2</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Actual_ERPM</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="3" t="n">
+        <v>-120000</v>
+      </c>
+      <c r="I123" s="3" t="n">
+        <v>120000</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>ERPM</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Actual_Duty</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I124" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Actual_InputVoltage</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr"/>
+    </row>
+    <row r="126"/>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV2_AC_DC_current</t>
+        </is>
+      </c>
+      <c r="B127" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x425</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_INV2</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Actual_ACCurrent</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>Apk</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Actual_DCCurrent</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I130" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr"/>
+    </row>
+    <row r="131"/>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV2_Temperatures</t>
+        </is>
+      </c>
+      <c r="B132" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x445</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_INV2</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Actual_TempController</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" s="3" t="n">
+        <v>-55</v>
+      </c>
+      <c r="I134" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Actual_TempMotor</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>-55</v>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Actual_FaultCode</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F136" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J136" s="3" t="n"/>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>0=NO_FAULT, 1=OVERVOLTAGE, 2=UNDERVOLTAGE, 3=DRV_ERROR, 4=ABS_MAX_OVERCURRENT, 5=CONTROLLER_OVERTEMPERATURE, 6=MOTOR_OVERTEMPERATURE, 7=SENSOR_WIRE_FAULT, 8=SENSOR_GENERAL_FAULT, 9=CAN_COMMAND_ERROR, 10=ANALOG_INPUT_ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="137"/>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV2_FOC</t>
+        </is>
+      </c>
+      <c r="B138" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x465</t>
+        </is>
+      </c>
+      <c r="C138" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_INV2</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Actual_FOC_id</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F140" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I140" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>Apk</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Actual_FOC_iq</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F141" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I141" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>Apk</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr"/>
+    </row>
+    <row r="142"/>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV2_MISC</t>
+        </is>
+      </c>
+      <c r="B143" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x485</t>
+        </is>
+      </c>
+      <c r="C143" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_INV2</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Actual_Throttle</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C145" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F145" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Actual_Brake</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C146" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K146" s="3" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Digital_output_4</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C147" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F147" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J147" s="3" t="n"/>
+      <c r="K147" s="3" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Digital_output_3</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C148" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J148" s="3" t="n"/>
+      <c r="K148" s="3" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Digital_output_2</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="C149" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F149" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J149" s="3" t="n"/>
+      <c r="K149" s="3" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Digital_output_1</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C150" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F150" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J150" s="3" t="n"/>
+      <c r="K150" s="3" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Digital_input_4</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" s="3" t="n"/>
+      <c r="K151" s="3" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Digital_input_3</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F152" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J152" s="3" t="n"/>
+      <c r="K152" s="3" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Digital_input_2</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" s="3" t="n"/>
+      <c r="K153" s="3" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Digital_input_1</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C154" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F154" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" s="3" t="n"/>
+      <c r="K154" s="3" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Drive_enable</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="C155" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F155" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J155" s="3" t="n"/>
+      <c r="K155" s="3" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Motor_temp_limit</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C156" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F156" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J156" s="3" t="n"/>
+      <c r="K156" s="3" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Motor_accel_limit</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="C157" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F157" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J157" s="3" t="n"/>
+      <c r="K157" s="3" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Input_voltage_limit</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="C158" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F158" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J158" s="3" t="n"/>
+      <c r="K158" s="3" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>INV2_IGBT_temp_limit</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="C159" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F159" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J159" s="3" t="n"/>
+      <c r="K159" s="3" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>INV2_IGBT_accel_limit</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="C160" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J160" s="3" t="n"/>
+      <c r="K160" s="3" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Drive_enable_limit</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="C161" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F161" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J161" s="3" t="n"/>
+      <c r="K161" s="3" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>INV2_DC_current_limit</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="C162" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F162" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G162" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J162" s="3" t="n"/>
+      <c r="K162" s="3" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Capacitor_temp_limit</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F163" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J163" s="3" t="n"/>
+      <c r="K163" s="3" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>INV2_Power_limit</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="C164" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F164" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J164" s="3" t="n"/>
+      <c r="K164" s="3" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>INV2_RPM_max_limit</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J165" s="3" t="n"/>
+      <c r="K165" s="3" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>INV2_RPM_min_limit</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C166" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F166" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J166" s="3" t="n"/>
+      <c r="K166" s="3" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>INV2_CAN_map_version</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F167" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="inlineStr"/>
+    </row>
+    <row r="168"/>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV2_TargetIq</t>
+        </is>
+      </c>
+      <c r="B169" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x3e5</t>
+        </is>
+      </c>
+      <c r="C169" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_INV2</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>INV2_ControlMode</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C171" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F171" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I171" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="K171" s="3" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>INV2_TargetIq</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C172" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F172" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G172" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I172" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>Apk</t>
+        </is>
+      </c>
+      <c r="K172" s="3" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>INV2_MotorPosition</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="C173" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F173" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G173" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" s="3" t="n">
+        <v>359</v>
+      </c>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="K173" s="3" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>INV2_isMotorStill</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="C174" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F174" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G174" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I174" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J174" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="K174" s="3" t="inlineStr"/>
+    </row>
+    <row r="175"/>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV2_MinMaxAcCurrent</t>
+        </is>
+      </c>
+      <c r="B176" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x4a5</t>
+        </is>
+      </c>
+      <c r="C176" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_INV2</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>INV2_MaxAcCurrent</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C178" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F178" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G178" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J178" s="3" t="inlineStr">
+        <is>
+          <t>Apk</t>
+        </is>
+      </c>
+      <c r="K178" s="3" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>INV2_AvailableMaxAcCurrent</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C179" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F179" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G179" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J179" s="3" t="inlineStr">
+        <is>
+          <t>Apk</t>
+        </is>
+      </c>
+      <c r="K179" s="3" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>INV2_MinAcCurrent</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C180" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F180" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G180" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I180" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>Apk</t>
+        </is>
+      </c>
+      <c r="K180" s="3" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>INV2_AvailableMinAcCurrent</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="C181" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F181" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G181" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I181" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" s="3" t="inlineStr">
+        <is>
+          <t>Apk</t>
+        </is>
+      </c>
+      <c r="K181" s="3" t="inlineStr"/>
+    </row>
+    <row r="182"/>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV2_MinMaxDcCurrent</t>
+        </is>
+      </c>
+      <c r="B183" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x4c5</t>
+        </is>
+      </c>
+      <c r="C183" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_INV2</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>INV2_MaxDcCurrent</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C185" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F185" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G185" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I185" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J185" s="3" t="inlineStr">
+        <is>
+          <t>Adc</t>
+        </is>
+      </c>
+      <c r="K185" s="3" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>INV2_AvailableMaxDcCurrent</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C186" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F186" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G186" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I186" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J186" s="3" t="inlineStr">
+        <is>
+          <t>Adc</t>
+        </is>
+      </c>
+      <c r="K186" s="3" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>INV2_MinDcCurrent</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C187" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F187" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G187" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I187" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" s="3" t="inlineStr">
+        <is>
+          <t>Adc</t>
+        </is>
+      </c>
+      <c r="K187" s="3" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>INV2_AvailableMinDcCurrent</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="C188" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F188" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G188" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I188" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" s="3" t="inlineStr">
+        <is>
+          <t>Adc</t>
+        </is>
+      </c>
+      <c r="K188" s="3" t="inlineStr"/>
+    </row>
+    <row r="189"/>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV2_SetDriveEnable</t>
+        </is>
+      </c>
+      <c r="B190" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x185</t>
+        </is>
+      </c>
+      <c r="C190" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K191" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>INV2_CMD_DriveEnable</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C192" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F192" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J192" s="3" t="n"/>
+      <c r="K192" s="3" t="inlineStr"/>
+    </row>
+    <row r="193"/>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV2_SetAcCurrent</t>
+        </is>
+      </c>
+      <c r="B194" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x25</t>
+        </is>
+      </c>
+      <c r="C194" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K195" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>INV2_CMD_TargetAcCurrent</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C196" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F196" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G196" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I196" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J196" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K196" s="3" t="inlineStr"/>
+    </row>
+    <row r="197"/>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV2_SetBrakeCurrent</t>
+        </is>
+      </c>
+      <c r="B198" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x45</t>
+        </is>
+      </c>
+      <c r="C198" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>INV2_CMD_TargetBrakeCurrent</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C200" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F200" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G200" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I200" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J200" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K200" s="3" t="inlineStr"/>
+    </row>
+    <row r="201"/>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV2_SetERPM</t>
+        </is>
+      </c>
+      <c r="B202" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x65</t>
+        </is>
+      </c>
+      <c r="C202" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K203" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>INV2_CMD_TargetSpeed</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C204" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F204" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="I204" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="J204" s="3" t="inlineStr">
+        <is>
+          <t>ERPM</t>
+        </is>
+      </c>
+      <c r="K204" s="3" t="inlineStr"/>
+    </row>
+    <row r="205"/>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV2_SetPosition</t>
+        </is>
+      </c>
+      <c r="B206" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x85</t>
+        </is>
+      </c>
+      <c r="C206" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K207" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>INV2_CMD_TargetPosition</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C208" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F208" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G208" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I208" s="3" t="n">
+        <v>359</v>
+      </c>
+      <c r="J208" s="3" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="K208" s="3" t="inlineStr"/>
+    </row>
+    <row r="209"/>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV2_SetRelCurrent</t>
+        </is>
+      </c>
+      <c r="B210" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0xa5</t>
+        </is>
+      </c>
+      <c r="C210" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K211" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>INV2_CMD_TargetRelativeCurrent</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C212" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F212" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G212" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" s="3" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I212" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J212" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K212" s="3" t="inlineStr"/>
+    </row>
+    <row r="213"/>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV2_SetRelBrakeCurrent</t>
+        </is>
+      </c>
+      <c r="B214" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0xc5</t>
+        </is>
+      </c>
+      <c r="C214" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K215" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>INV2_CMD_TgtRelBrakeCurrent</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C216" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F216" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G216" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I216" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J216" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K216" s="3" t="inlineStr"/>
+    </row>
+    <row r="217"/>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV2_SetDigOutput</t>
+        </is>
+      </c>
+      <c r="B218" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0xe5</t>
+        </is>
+      </c>
+      <c r="C218" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K219" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>INV2_CMD_SetDigOutput4</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C220" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F220" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G220" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J220" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="K220" s="3" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>INV2_CMD_SetDigOutput3</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C221" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F221" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G221" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I221" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J221" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="K221" s="3" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>INV2_CMD_SetDigOutput2</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C222" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F222" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G222" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I222" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J222" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="K222" s="3" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>INV2_CMD_SetDigOutput1</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C223" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F223" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G223" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I223" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J223" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="K223" s="3" t="inlineStr"/>
+    </row>
+    <row r="224"/>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV2_SetMaxAcCurrent</t>
+        </is>
+      </c>
+      <c r="B225" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x105</t>
+        </is>
+      </c>
+      <c r="C225" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K226" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>INV2_CMD_MaxAcCurrent</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C227" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F227" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G227" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I227" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J227" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K227" s="3" t="inlineStr"/>
+    </row>
+    <row r="228"/>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV2_SetMaxAcBrakeCurrent</t>
+        </is>
+      </c>
+      <c r="B229" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x125</t>
+        </is>
+      </c>
+      <c r="C229" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K230" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>INV2_CMD_MaxAcBrakeCurrent</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C231" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F231" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G231" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I231" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K231" s="3" t="inlineStr"/>
+    </row>
+    <row r="232"/>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV2_SetMaxDcCurrent</t>
+        </is>
+      </c>
+      <c r="B233" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x145</t>
+        </is>
+      </c>
+      <c r="C233" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K234" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>INV2_CMD_MaxDcCurrent</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C235" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F235" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G235" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I235" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="J235" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K235" s="3" t="inlineStr"/>
+    </row>
+    <row r="236"/>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV2_SetMaxDcBrakeCurrent</t>
+        </is>
+      </c>
+      <c r="B237" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x165</t>
+        </is>
+      </c>
+      <c r="C237" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): HV500_commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J238" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K238" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>INV2_CMD_MaxDcBrakeCurrent</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C239" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F239" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G239" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" s="3" t="n">
+        <v>-850</v>
+      </c>
+      <c r="I239" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K239" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -1384,8 +1384,8 @@
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="157" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="376" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>ï¿½</t>
+          <t>Âºc</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr"/>
@@ -2053,7 +2053,11 @@
         <v>255</v>
       </c>
       <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>0=None, 1=OVER-VOLTAGE, 2=UNDER-VOLTAGE, 3=DRIVER-FAULT, 4=OVER-CURRENT, 5=MOSFET-OVER-TEMP, 6=MOTOR-OVER-TEMP, 7=GATE-DRIVE-OVER-VOLTAGE, 8=GATE-DRIVE-UNDER-VOLTAGE, 9=MCU-UNDER-VOLTAGE, 10=REBOOTING-FROM-WATCHDOG, 11=ENCODER-FAULT, 12=MIN-ENCODER-LIMIT-EXCEEDED, 13=MAX-ENCODER-LIMIT-EXCEEDED, 14=FLASH-FAULT, 15=HIGH-OFFSET-CURRENT-SENSOR1, 16=HIGH-OFFSET-CURRENT-SENSOR2</t>
+        </is>
+      </c>
     </row>
     <row r="20"/>
     <row r="21">
@@ -2160,7 +2164,7 @@
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>ï¿½</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr"/>
@@ -2442,7 +2446,7 @@
       <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>ï¿½</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr"/>
@@ -2552,7 +2556,7 @@
       <c r="I37" s="3" t="n"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>ï¿½</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr"/>
@@ -2662,7 +2666,7 @@
       <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>º</t>
+          <t>Âº</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr"/>
@@ -3419,7 +3423,7 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>ï¿½</t>
+          <t>rad</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr"/>
@@ -3458,7 +3462,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>ï¿½</t>
+          <t>rad</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr"/>
@@ -3794,7 +3798,7 @@
       <c r="I77" s="3" t="n"/>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>ï¿½/s</t>
+          <t>m/s2</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr"/>
@@ -5281,7 +5285,7 @@
       <c r="J125" s="3" t="n"/>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>0=None, 1=ACU, 2=ZED, 3=Steering, 4=Planner, 5=SLAM, 6=P-Puma, 7=IMU</t>
+          <t>0=None, 1=RES, 2=ACU, 3=ZED, 4=Steering_error, 5=Steering_timeout, 6=Planner, 7=SLAM, 8=P-Puma, 9=IMU</t>
         </is>
       </c>
     </row>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -5574,7 +5574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1076"/>
+  <dimension ref="A1:K1080"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>0=PRECHARGE OFF, 1=BALANCING ON</t>
+          <t>0=open/de-energize, 1=close/energize contactors</t>
         </is>
       </c>
     </row>
@@ -38403,7 +38403,7 @@
     <row r="1057">
       <c r="A1057" s="3" t="inlineStr">
         <is>
-          <t>APPS1</t>
+          <t>apps1_raw</t>
         </is>
       </c>
       <c r="B1057" s="3" t="n">
@@ -38438,7 +38438,7 @@
     <row r="1058">
       <c r="A1058" s="3" t="inlineStr">
         <is>
-          <t>APPS2</t>
+          <t>apps2_raw</t>
         </is>
       </c>
       <c r="B1058" s="3" t="n">
@@ -38548,7 +38548,7 @@
     <row r="1062">
       <c r="A1062" s="3" t="inlineStr">
         <is>
-          <t>Ignition</t>
+          <t>ignition_switch_raw</t>
         </is>
       </c>
       <c r="B1062" s="3" t="n">
@@ -38579,7 +38579,7 @@
     <row r="1063">
       <c r="A1063" s="3" t="inlineStr">
         <is>
-          <t>Ready_To_Drive</t>
+          <t>r2d_button_raw</t>
         </is>
       </c>
       <c r="B1063" s="3" t="n">
@@ -38965,6 +38965,116 @@
       <c r="K1076" s="3" t="inlineStr">
         <is>
           <t>0=CHARGING OFF, 1=CHARGING ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077"/>
+    <row r="1078">
+      <c r="A1078" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_state</t>
+        </is>
+      </c>
+      <c r="B1078" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x750</t>
+        </is>
+      </c>
+      <c r="C1078" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B1079" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C1079" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D1079" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E1079" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F1079" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G1079" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H1079" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I1079" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J1079" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K1079" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="3" t="inlineStr">
+        <is>
+          <t>vcu_state</t>
+        </is>
+      </c>
+      <c r="B1080" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1080" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1080" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E1080" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F1080" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1080" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1080" s="3" t="n"/>
+      <c r="I1080" s="3" t="n"/>
+      <c r="J1080" s="3" t="n"/>
+      <c r="K1080" s="3" t="inlineStr">
+        <is>
+          <t>0=STATE_INIT,, 1=STATE_SHUTDOWN, 2=STATE_STANDBY, 3=STATE_PRECHARGE, 4=STATE_WAITING_FOR_R2D_MANUAL, 5=STATE_WAITING_FOR_R2D_AUTO, 6=STATE_READY_MANUAL, 7=STATE_READY_AUTONOMOUS, 8=STATE_AS_EMERGENCY</t>
         </is>
       </c>
     </row>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -38972,7 +38972,7 @@
     <row r="1078">
       <c r="A1078" s="1" t="inlineStr">
         <is>
-          <t>Message: VCU_state</t>
+          <t>Message: VCU_states</t>
         </is>
       </c>
       <c r="B1078" s="1" t="inlineStr">

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -24626,7 +24626,7 @@
       <c r="J616" s="3" t="n"/>
       <c r="K616" s="3" t="inlineStr">
         <is>
-          <t>0=START, 1=OPEN_ALL, 2=SWITCH_HVNEG, 3=WAIT_FOR_AIR_NEG_TO_CLOSE, 4=CHECKING_AIR_NEG_IS_CLOSED, 5=SWITCH_PRECHARGE, 6=WAIT_FOR_PRECHARGE_TO_CLOSE, 7=CHECKING_PRECHARGE_IS_CLOSED, 8=VERIFY_CURRENT, 9=VERIFY_BUS_VOLT, 10=SWITCH_HVPOS, 11=WAIT_FOR_AIR_POS_TO_CLOSE, 12=CHECKING_AIR_POS_IS_CLOSED, 13=TURN_OFF_PRECHARGE, 14=WAIT_FOR_PRECHARGE_TO_OPEN, 15=CHECKING_PRECHARGE_IS_OPEN, 16=END, 17=WRONG, 18=KILL, 19=RX_CAN</t>
+          <t>0=START, 1=OPEN_ALL, 2=SWITCH_HVNEG, 3=WAIT_FOR_AIR_NEG_TO_CLOSE, 4=CHECKING_AIR_NEG_IS_CLOSED, 5=SWITCH_PRECHARGE, 6=WAIT_FOR_PRECHARGE_TO_CLOSE, 7=CHECKING_PRECHARGE_IS_CLOSED, 8=VERIFY_CURRENT, 9=VERIFY_BUS_VOLT, 10=SWITCH_HVPOS, 11=WAIT_FOR_AIR_POS_TO_CLOSE, 12=CHECKING_AIR_POS_IS_CLOSED, 13=TURN_OFF_PRECHARGE, 14=WAIT_FOR_PRECHARGE_TO_OPEN, 15=CHECKING_PRECHARGE_IS_OPEN, 16=HV-ON, 17=WRONG, 18=KILL, 19=RX_CAN</t>
         </is>
       </c>
     </row>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -1380,10 +1380,10 @@
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="6" customWidth="1" min="10" max="10"/>
     <col width="376" customWidth="1" min="11" max="11"/>
   </cols>
@@ -1871,14 +1871,14 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>16</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E15" s="3" t="b">
@@ -1910,34 +1910,34 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>16</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E16" s="3" t="b">
         <v>1</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1890</v>
+        <v>0.0529100529</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-320000</v>
+        <v>-1693.121693</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>320000</v>
+        <v>1693.121693</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>ERPM</t>
+          <t>RPM</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr"/>
@@ -1949,14 +1949,14 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>16</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E17" s="3" t="b">
@@ -1984,18 +1984,18 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Driver_Temp</t>
+          <t>Motor_Temperature</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>8</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E18" s="3" t="b">
@@ -2027,14 +2027,14 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>8</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E19" s="3" t="b">
@@ -2050,7 +2050,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>255</v>
+        <v>7</v>
       </c>
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
@@ -2155,13 +2155,17 @@
         <v>1</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1000</v>
+        <v>0.0001</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
+      <c r="H23" s="3" t="n">
+        <v>-36000</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>36000</v>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
           <t>deg</t>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -1984,7 +1984,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Motor_Temperature</t>
+          <t>Driver_Temp</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -5578,7 +5578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1193"/>
+  <dimension ref="A1:K1200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -24415,7 +24415,7 @@
       <c r="J609" s="3" t="n"/>
       <c r="K609" s="3" t="inlineStr">
         <is>
-          <t>0=START, 1=OPEN_ALL, 2=SWITCH_HVNEG, 3=WAIT_FOR_AIR_NEG_TO_CLOSE, 4=CHECKING_AIR_NEG_IS_CLOSED, 5=SWITCH_PRECHARGE, 6=WAIT_FOR_PRECHARGE_TO_CLOSE, 7=CHECKING_PRECHARGE_IS_CLOSED, 8=VERIFY_CURRENT, 9=VERIFY_BUS_VOLT, 10=SWITCH_HVPOS, 11=WAIT_FOR_AIR_POS_TO_CLOSE, 12=CHECKING_AIR_POS_IS_CLOSED, 13=TURN_OFF_PRECHARGE, 14=WAIT_FOR_PRECHARGE_TO_OPEN, 15=CHECKING_PRECHARGE_IS_OPEN, 16=HV-ON, 17=WRONG, 18=KILL, 19=RX_CAN</t>
+          <t>0=START, 1=OPEN_ALL, 2=SWITCH_HVNEG, 3=WAIT_FOR_AIR_NEG_TO_CLOSE, 4=CHECKING_AIR_NEG_IS_CLOSED, 5=SWITCH_PRECHARGE, 6=WAIT_FOR_PRECHARGE_TO_CLOSE, 7=CHECKING_PRECHARGE_IS_CLOSED, 8=VERIFY_CURRENT, 9=VERIFY_BUS_VOLT, 10=SWITCH_HVPOS, 11=WAIT_FOR_AIR_POS_TO_CLOSE, 12=CHECKING_AIR_POS_IS_CLOSED, 13=TURN_OFF_PRECHARGE, 14=WAIT_FOR_PRECHARGE_TO_OPEN, 15=CHECKING_PRECHARGE_IS_OPEN, 16=HV_ON, 17=WRONG, 18=KILL, 19=RX_CAN</t>
         </is>
       </c>
     </row>
@@ -42618,6 +42618,221 @@
         </is>
       </c>
       <c r="K1193" s="3" t="inlineStr"/>
+    </row>
+    <row r="1194"/>
+    <row r="1195">
+      <c r="A1195" s="1" t="inlineStr">
+        <is>
+          <t>Message: Slave_10_MSC_ID_1</t>
+        </is>
+      </c>
+      <c r="B1195" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x644</t>
+        </is>
+      </c>
+      <c r="C1195" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): AMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B1196" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C1196" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D1196" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E1196" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F1196" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G1196" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H1196" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I1196" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J1196" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K1196" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="3" t="inlineStr">
+        <is>
+          <t>module_voltage_sum</t>
+        </is>
+      </c>
+      <c r="B1197" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1197" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1197" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E1197" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F1197" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G1197" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1197" s="3" t="n"/>
+      <c r="I1197" s="3" t="n"/>
+      <c r="J1197" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K1197" s="3" t="inlineStr"/>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="3" t="inlineStr">
+        <is>
+          <t>module_voltage_avg</t>
+        </is>
+      </c>
+      <c r="B1198" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1198" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1198" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E1198" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F1198" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G1198" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1198" s="3" t="n"/>
+      <c r="I1198" s="3" t="n"/>
+      <c r="J1198" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K1198" s="3" t="inlineStr"/>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="3" t="inlineStr">
+        <is>
+          <t>module_voltage_min</t>
+        </is>
+      </c>
+      <c r="B1199" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1199" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1199" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E1199" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F1199" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G1199" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1199" s="3" t="n"/>
+      <c r="I1199" s="3" t="n"/>
+      <c r="J1199" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K1199" s="3" t="inlineStr"/>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="3" t="inlineStr">
+        <is>
+          <t>module_voltage_max</t>
+        </is>
+      </c>
+      <c r="B1200" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C1200" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1200" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E1200" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F1200" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G1200" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1200" s="3" t="n"/>
+      <c r="I1200" s="3" t="n"/>
+      <c r="J1200" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K1200" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -441,10 +441,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -1360,6 +1360,555 @@
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV1_Temperatures</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x444</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): FSIC_INV1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>INV1_TempInverter</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>-55</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>INV1_TempMotor</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>-55</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Message: INV2_Temperatures</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x445</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): FSIC_INV2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>INV2_TempInverter</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>-55</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>INV2_TempMotor</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>-55</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Message: PDM_LV</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x210</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): PDM</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>LV_Voltage_mV</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3" t="n"/>
+      <c r="I44" s="3" t="n"/>
+      <c r="J44" s="3" t="n"/>
+      <c r="K44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Message: PDM_Cooling</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x220</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): PDM</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>WaterPump_PWM</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3" t="n"/>
+      <c r="I48" s="3" t="n"/>
+      <c r="J48" s="3" t="n"/>
+      <c r="K48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>CoolingFan_PWM</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3" t="n"/>
+      <c r="I49" s="3" t="n"/>
+      <c r="J49" s="3" t="n"/>
+      <c r="K49" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -444,7 +444,7 @@
   <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -1365,7 +1365,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Message: INV1_Temperatures</t>
+          <t>Message: VCU_INV1_Temperatures</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>Sender(s): FSIC_INV1</t>
+          <t>Sender(s): VCU</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Message: INV2_Temperatures</t>
+          <t>Message: VCU_INV2_Temperatures</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>Sender(s): FSIC_INV2</t>
+          <t>Sender(s): VCU</t>
         </is>
       </c>
     </row>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -1820,7 +1820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1200"/>
+  <dimension ref="A1:K1204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -39075,6 +39075,120 @@
         </is>
       </c>
       <c r="K1200" s="3" t="inlineStr"/>
+    </row>
+    <row r="1201"/>
+    <row r="1202">
+      <c r="A1202" s="1" t="inlineStr">
+        <is>
+          <t>Message: AMS_SDC_Feedback</t>
+        </is>
+      </c>
+      <c r="B1202" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x709</t>
+        </is>
+      </c>
+      <c r="C1202" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): AMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B1203" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C1203" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D1203" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E1203" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F1203" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G1203" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H1203" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I1203" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J1203" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K1203" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="3" t="inlineStr">
+        <is>
+          <t>SDC_State</t>
+        </is>
+      </c>
+      <c r="B1204" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1204" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1204" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E1204" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F1204" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1204" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1204" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1204" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1204" s="3" t="n"/>
+      <c r="K1204" s="3" t="inlineStr">
+        <is>
+          <t>0=There is no SDC on the AMS, 1=We have SDC on the AMS</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -6039,7 +6039,7 @@
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="64" customWidth="1" min="11" max="11"/>
+    <col width="65" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15941,7 +15941,11 @@
         <v>255</v>
       </c>
       <c r="J315" s="3" t="n"/>
-      <c r="K315" s="3" t="inlineStr"/>
+      <c r="K315" s="3" t="inlineStr">
+        <is>
+          <t>0=Starting to charg, 1=Battery protection, charger close output</t>
+        </is>
+      </c>
     </row>
     <row r="316"/>
     <row r="317">
